--- a/Excel/Pivot Table clean dataset sales 1.xlsx
+++ b/Excel/Pivot Table clean dataset sales 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ACA4E9-D0C6-4F7F-89AC-AB2EC0851C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9F3DB1-D17B-4E79-9A2F-EFA27AA81D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B30FDB32-350C-4338-B263-7714CC58AC36}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4253,7 +4253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -4292,14 +4292,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="117">
+  <dxfs count="69">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -4308,6 +4314,72 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -4382,6 +4454,72 @@
       <alignment vertical="center"/>
     </dxf>
     <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -4434,15 +4572,6 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -4634,282 +4763,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
     </dxf>
     <dxf>
       <border>
@@ -33947,4319 +33800,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3C16518-6C6B-401F-9B59-4FD81C70871C}" name="PivotTable10" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
-  <location ref="A100:B113" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField dataField="1" showAll="0">
-      <items count="1301">
-        <item x="0"/>
-        <item x="9"/>
-        <item x="99"/>
-        <item x="999"/>
-        <item x="1000"/>
-        <item x="1001"/>
-        <item x="1002"/>
-        <item x="1003"/>
-        <item x="1004"/>
-        <item x="1005"/>
-        <item x="1006"/>
-        <item x="1007"/>
-        <item x="1008"/>
-        <item x="100"/>
-        <item x="1009"/>
-        <item x="1010"/>
-        <item x="1011"/>
-        <item x="1012"/>
-        <item x="1013"/>
-        <item x="1014"/>
-        <item x="1015"/>
-        <item x="1016"/>
-        <item x="1017"/>
-        <item x="1018"/>
-        <item x="101"/>
-        <item x="1019"/>
-        <item x="1020"/>
-        <item x="1021"/>
-        <item x="1022"/>
-        <item x="1023"/>
-        <item x="1024"/>
-        <item x="1025"/>
-        <item x="1026"/>
-        <item x="1027"/>
-        <item x="1028"/>
-        <item x="102"/>
-        <item x="1029"/>
-        <item x="1030"/>
-        <item x="1031"/>
-        <item x="1032"/>
-        <item x="1033"/>
-        <item x="1034"/>
-        <item x="1035"/>
-        <item x="1036"/>
-        <item x="1037"/>
-        <item x="1038"/>
-        <item x="103"/>
-        <item x="1039"/>
-        <item x="1040"/>
-        <item x="1041"/>
-        <item x="1042"/>
-        <item x="1043"/>
-        <item x="1044"/>
-        <item x="1045"/>
-        <item x="1046"/>
-        <item x="1047"/>
-        <item x="1048"/>
-        <item x="104"/>
-        <item x="1049"/>
-        <item x="1050"/>
-        <item x="1051"/>
-        <item x="1052"/>
-        <item x="1053"/>
-        <item x="1054"/>
-        <item x="1055"/>
-        <item x="1056"/>
-        <item x="1057"/>
-        <item x="1058"/>
-        <item x="105"/>
-        <item x="1059"/>
-        <item x="1060"/>
-        <item x="1061"/>
-        <item x="1062"/>
-        <item x="1063"/>
-        <item x="1064"/>
-        <item x="1065"/>
-        <item x="1066"/>
-        <item x="1067"/>
-        <item x="1068"/>
-        <item x="106"/>
-        <item x="1069"/>
-        <item x="1070"/>
-        <item x="1071"/>
-        <item x="1072"/>
-        <item x="1073"/>
-        <item x="1074"/>
-        <item x="1075"/>
-        <item x="1076"/>
-        <item x="1077"/>
-        <item x="1078"/>
-        <item x="107"/>
-        <item x="1079"/>
-        <item x="1080"/>
-        <item x="1081"/>
-        <item x="1082"/>
-        <item x="1083"/>
-        <item x="1084"/>
-        <item x="1085"/>
-        <item x="1086"/>
-        <item x="1087"/>
-        <item x="1088"/>
-        <item x="108"/>
-        <item x="1089"/>
-        <item x="1090"/>
-        <item x="1091"/>
-        <item x="1092"/>
-        <item x="1093"/>
-        <item x="1094"/>
-        <item x="1095"/>
-        <item x="1096"/>
-        <item x="1097"/>
-        <item x="1098"/>
-        <item x="10"/>
-        <item x="109"/>
-        <item x="1099"/>
-        <item x="1100"/>
-        <item x="1101"/>
-        <item x="1102"/>
-        <item x="1103"/>
-        <item x="1104"/>
-        <item x="1105"/>
-        <item x="1106"/>
-        <item x="1107"/>
-        <item x="1108"/>
-        <item x="110"/>
-        <item x="1109"/>
-        <item x="1110"/>
-        <item x="1111"/>
-        <item x="1112"/>
-        <item x="1113"/>
-        <item x="1114"/>
-        <item x="1115"/>
-        <item x="1116"/>
-        <item x="1117"/>
-        <item x="1118"/>
-        <item x="111"/>
-        <item x="1119"/>
-        <item x="1120"/>
-        <item x="1121"/>
-        <item x="1122"/>
-        <item x="1123"/>
-        <item x="1124"/>
-        <item x="1125"/>
-        <item x="1126"/>
-        <item x="1127"/>
-        <item x="1128"/>
-        <item x="112"/>
-        <item x="1129"/>
-        <item x="1130"/>
-        <item x="1131"/>
-        <item x="1132"/>
-        <item x="1133"/>
-        <item x="1134"/>
-        <item x="1135"/>
-        <item x="1136"/>
-        <item x="1137"/>
-        <item x="1138"/>
-        <item x="113"/>
-        <item x="1139"/>
-        <item x="1140"/>
-        <item x="1141"/>
-        <item x="1142"/>
-        <item x="1143"/>
-        <item x="1144"/>
-        <item x="1145"/>
-        <item x="1146"/>
-        <item x="1147"/>
-        <item x="1148"/>
-        <item x="114"/>
-        <item x="1149"/>
-        <item x="1150"/>
-        <item x="1151"/>
-        <item x="1152"/>
-        <item x="1153"/>
-        <item x="1154"/>
-        <item x="1155"/>
-        <item x="1156"/>
-        <item x="1157"/>
-        <item x="1158"/>
-        <item x="115"/>
-        <item x="1159"/>
-        <item x="1160"/>
-        <item x="1161"/>
-        <item x="1162"/>
-        <item x="1163"/>
-        <item x="1164"/>
-        <item x="1165"/>
-        <item x="1166"/>
-        <item x="1167"/>
-        <item x="1168"/>
-        <item x="116"/>
-        <item x="1169"/>
-        <item x="1170"/>
-        <item x="1171"/>
-        <item x="1172"/>
-        <item x="1173"/>
-        <item x="1174"/>
-        <item x="1175"/>
-        <item x="1176"/>
-        <item x="1177"/>
-        <item x="1178"/>
-        <item x="117"/>
-        <item x="1179"/>
-        <item x="1180"/>
-        <item x="1181"/>
-        <item x="1182"/>
-        <item x="1183"/>
-        <item x="1184"/>
-        <item x="1185"/>
-        <item x="1186"/>
-        <item x="1187"/>
-        <item x="1188"/>
-        <item x="118"/>
-        <item x="1189"/>
-        <item x="1190"/>
-        <item x="1191"/>
-        <item x="1192"/>
-        <item x="1193"/>
-        <item x="1194"/>
-        <item x="1195"/>
-        <item x="1196"/>
-        <item x="1197"/>
-        <item x="1198"/>
-        <item x="11"/>
-        <item x="119"/>
-        <item x="1199"/>
-        <item x="1200"/>
-        <item x="1201"/>
-        <item x="1202"/>
-        <item x="1203"/>
-        <item x="1204"/>
-        <item x="1205"/>
-        <item x="1206"/>
-        <item x="1207"/>
-        <item x="1208"/>
-        <item x="120"/>
-        <item x="1209"/>
-        <item x="1210"/>
-        <item x="1211"/>
-        <item x="1212"/>
-        <item x="1213"/>
-        <item x="1214"/>
-        <item x="1215"/>
-        <item x="1216"/>
-        <item x="1217"/>
-        <item x="1218"/>
-        <item x="121"/>
-        <item x="1219"/>
-        <item x="1220"/>
-        <item x="1221"/>
-        <item x="1222"/>
-        <item x="1223"/>
-        <item x="1224"/>
-        <item x="1225"/>
-        <item x="1226"/>
-        <item x="1227"/>
-        <item x="1228"/>
-        <item x="122"/>
-        <item x="1229"/>
-        <item x="1230"/>
-        <item x="1231"/>
-        <item x="1232"/>
-        <item x="1233"/>
-        <item x="1234"/>
-        <item x="1235"/>
-        <item x="1236"/>
-        <item x="1237"/>
-        <item x="1238"/>
-        <item x="123"/>
-        <item x="1239"/>
-        <item x="1240"/>
-        <item x="1241"/>
-        <item x="1242"/>
-        <item x="1243"/>
-        <item x="1244"/>
-        <item x="1245"/>
-        <item x="1246"/>
-        <item x="1247"/>
-        <item x="1248"/>
-        <item x="124"/>
-        <item x="1249"/>
-        <item x="1250"/>
-        <item x="1251"/>
-        <item x="1252"/>
-        <item x="1253"/>
-        <item x="1254"/>
-        <item x="1255"/>
-        <item x="1256"/>
-        <item x="1257"/>
-        <item x="1258"/>
-        <item x="125"/>
-        <item x="1259"/>
-        <item x="1260"/>
-        <item x="1261"/>
-        <item x="1262"/>
-        <item x="1263"/>
-        <item x="1264"/>
-        <item x="1265"/>
-        <item x="1266"/>
-        <item x="1267"/>
-        <item x="1268"/>
-        <item x="126"/>
-        <item x="1269"/>
-        <item x="1270"/>
-        <item x="1271"/>
-        <item x="1272"/>
-        <item x="1273"/>
-        <item x="1274"/>
-        <item x="1275"/>
-        <item x="1276"/>
-        <item x="1277"/>
-        <item x="1278"/>
-        <item x="127"/>
-        <item x="1279"/>
-        <item x="1280"/>
-        <item x="1281"/>
-        <item x="1282"/>
-        <item x="1283"/>
-        <item x="1284"/>
-        <item x="1285"/>
-        <item x="1286"/>
-        <item x="1287"/>
-        <item x="1288"/>
-        <item x="128"/>
-        <item x="1289"/>
-        <item x="1290"/>
-        <item x="1291"/>
-        <item x="1292"/>
-        <item x="1293"/>
-        <item x="1294"/>
-        <item x="1295"/>
-        <item x="1296"/>
-        <item x="1297"/>
-        <item x="1298"/>
-        <item x="12"/>
-        <item x="129"/>
-        <item x="1299"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="13"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="14"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="15"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="16"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="17"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="18"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="20"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="21"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="22"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="23"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="24"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="25"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="26"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="27"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="28"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="30"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="31"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="32"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="33"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="34"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="35"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item x="368"/>
-        <item x="36"/>
-        <item x="369"/>
-        <item x="370"/>
-        <item x="371"/>
-        <item x="372"/>
-        <item x="373"/>
-        <item x="374"/>
-        <item x="375"/>
-        <item x="376"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="37"/>
-        <item x="379"/>
-        <item x="380"/>
-        <item x="381"/>
-        <item x="382"/>
-        <item x="383"/>
-        <item x="384"/>
-        <item x="385"/>
-        <item x="386"/>
-        <item x="387"/>
-        <item x="388"/>
-        <item x="38"/>
-        <item x="389"/>
-        <item x="390"/>
-        <item x="391"/>
-        <item x="392"/>
-        <item x="393"/>
-        <item x="394"/>
-        <item x="395"/>
-        <item x="396"/>
-        <item x="397"/>
-        <item x="398"/>
-        <item x="3"/>
-        <item x="39"/>
-        <item x="399"/>
-        <item x="400"/>
-        <item x="401"/>
-        <item x="402"/>
-        <item x="403"/>
-        <item x="404"/>
-        <item x="405"/>
-        <item x="406"/>
-        <item x="407"/>
-        <item x="408"/>
-        <item x="40"/>
-        <item x="409"/>
-        <item x="410"/>
-        <item x="411"/>
-        <item x="412"/>
-        <item x="413"/>
-        <item x="414"/>
-        <item x="415"/>
-        <item x="416"/>
-        <item x="417"/>
-        <item x="418"/>
-        <item x="41"/>
-        <item x="419"/>
-        <item x="420"/>
-        <item x="421"/>
-        <item x="422"/>
-        <item x="423"/>
-        <item x="424"/>
-        <item x="425"/>
-        <item x="426"/>
-        <item x="427"/>
-        <item x="428"/>
-        <item x="42"/>
-        <item x="429"/>
-        <item x="430"/>
-        <item x="431"/>
-        <item x="432"/>
-        <item x="433"/>
-        <item x="434"/>
-        <item x="435"/>
-        <item x="436"/>
-        <item x="437"/>
-        <item x="438"/>
-        <item x="43"/>
-        <item x="439"/>
-        <item x="440"/>
-        <item x="441"/>
-        <item x="442"/>
-        <item x="443"/>
-        <item x="444"/>
-        <item x="445"/>
-        <item x="446"/>
-        <item x="447"/>
-        <item x="448"/>
-        <item x="44"/>
-        <item x="449"/>
-        <item x="450"/>
-        <item x="451"/>
-        <item x="452"/>
-        <item x="453"/>
-        <item x="454"/>
-        <item x="455"/>
-        <item x="456"/>
-        <item x="457"/>
-        <item x="458"/>
-        <item x="45"/>
-        <item x="459"/>
-        <item x="460"/>
-        <item x="461"/>
-        <item x="462"/>
-        <item x="463"/>
-        <item x="464"/>
-        <item x="465"/>
-        <item x="466"/>
-        <item x="467"/>
-        <item x="468"/>
-        <item x="46"/>
-        <item x="469"/>
-        <item x="470"/>
-        <item x="471"/>
-        <item x="472"/>
-        <item x="473"/>
-        <item x="474"/>
-        <item x="475"/>
-        <item x="476"/>
-        <item x="477"/>
-        <item x="478"/>
-        <item x="47"/>
-        <item x="479"/>
-        <item x="480"/>
-        <item x="481"/>
-        <item x="482"/>
-        <item x="483"/>
-        <item x="484"/>
-        <item x="485"/>
-        <item x="486"/>
-        <item x="487"/>
-        <item x="488"/>
-        <item x="48"/>
-        <item x="489"/>
-        <item x="490"/>
-        <item x="491"/>
-        <item x="492"/>
-        <item x="493"/>
-        <item x="494"/>
-        <item x="495"/>
-        <item x="496"/>
-        <item x="497"/>
-        <item x="498"/>
-        <item x="4"/>
-        <item x="49"/>
-        <item x="499"/>
-        <item x="500"/>
-        <item x="501"/>
-        <item x="502"/>
-        <item x="503"/>
-        <item x="504"/>
-        <item x="505"/>
-        <item x="506"/>
-        <item x="507"/>
-        <item x="508"/>
-        <item x="50"/>
-        <item x="509"/>
-        <item x="510"/>
-        <item x="511"/>
-        <item x="512"/>
-        <item x="513"/>
-        <item x="514"/>
-        <item x="515"/>
-        <item x="516"/>
-        <item x="517"/>
-        <item x="518"/>
-        <item x="51"/>
-        <item x="519"/>
-        <item x="520"/>
-        <item x="521"/>
-        <item x="522"/>
-        <item x="523"/>
-        <item x="524"/>
-        <item x="525"/>
-        <item x="526"/>
-        <item x="527"/>
-        <item x="528"/>
-        <item x="52"/>
-        <item x="529"/>
-        <item x="530"/>
-        <item x="531"/>
-        <item x="532"/>
-        <item x="533"/>
-        <item x="534"/>
-        <item x="535"/>
-        <item x="536"/>
-        <item x="537"/>
-        <item x="538"/>
-        <item x="53"/>
-        <item x="539"/>
-        <item x="540"/>
-        <item x="541"/>
-        <item x="542"/>
-        <item x="543"/>
-        <item x="544"/>
-        <item x="545"/>
-        <item x="546"/>
-        <item x="547"/>
-        <item x="548"/>
-        <item x="54"/>
-        <item x="549"/>
-        <item x="550"/>
-        <item x="551"/>
-        <item x="552"/>
-        <item x="553"/>
-        <item x="554"/>
-        <item x="555"/>
-        <item x="556"/>
-        <item x="557"/>
-        <item x="558"/>
-        <item x="55"/>
-        <item x="559"/>
-        <item x="560"/>
-        <item x="561"/>
-        <item x="562"/>
-        <item x="563"/>
-        <item x="564"/>
-        <item x="565"/>
-        <item x="566"/>
-        <item x="567"/>
-        <item x="568"/>
-        <item x="56"/>
-        <item x="569"/>
-        <item x="570"/>
-        <item x="571"/>
-        <item x="572"/>
-        <item x="573"/>
-        <item x="574"/>
-        <item x="575"/>
-        <item x="576"/>
-        <item x="577"/>
-        <item x="578"/>
-        <item x="57"/>
-        <item x="579"/>
-        <item x="580"/>
-        <item x="581"/>
-        <item x="582"/>
-        <item x="583"/>
-        <item x="584"/>
-        <item x="585"/>
-        <item x="586"/>
-        <item x="587"/>
-        <item x="588"/>
-        <item x="58"/>
-        <item x="589"/>
-        <item x="590"/>
-        <item x="591"/>
-        <item x="592"/>
-        <item x="593"/>
-        <item x="594"/>
-        <item x="595"/>
-        <item x="596"/>
-        <item x="597"/>
-        <item x="598"/>
-        <item x="5"/>
-        <item x="59"/>
-        <item x="599"/>
-        <item x="600"/>
-        <item x="601"/>
-        <item x="602"/>
-        <item x="603"/>
-        <item x="604"/>
-        <item x="605"/>
-        <item x="606"/>
-        <item x="607"/>
-        <item x="608"/>
-        <item x="60"/>
-        <item x="609"/>
-        <item x="610"/>
-        <item x="611"/>
-        <item x="612"/>
-        <item x="613"/>
-        <item x="614"/>
-        <item x="615"/>
-        <item x="616"/>
-        <item x="617"/>
-        <item x="618"/>
-        <item x="61"/>
-        <item x="619"/>
-        <item x="620"/>
-        <item x="621"/>
-        <item x="622"/>
-        <item x="623"/>
-        <item x="624"/>
-        <item x="625"/>
-        <item x="626"/>
-        <item x="627"/>
-        <item x="628"/>
-        <item x="62"/>
-        <item x="629"/>
-        <item x="630"/>
-        <item x="631"/>
-        <item x="632"/>
-        <item x="633"/>
-        <item x="634"/>
-        <item x="635"/>
-        <item x="636"/>
-        <item x="637"/>
-        <item x="638"/>
-        <item x="63"/>
-        <item x="639"/>
-        <item x="640"/>
-        <item x="641"/>
-        <item x="642"/>
-        <item x="643"/>
-        <item x="644"/>
-        <item x="645"/>
-        <item x="646"/>
-        <item x="647"/>
-        <item x="648"/>
-        <item x="64"/>
-        <item x="649"/>
-        <item x="650"/>
-        <item x="651"/>
-        <item x="652"/>
-        <item x="653"/>
-        <item x="654"/>
-        <item x="655"/>
-        <item x="656"/>
-        <item x="657"/>
-        <item x="658"/>
-        <item x="65"/>
-        <item x="659"/>
-        <item x="660"/>
-        <item x="661"/>
-        <item x="662"/>
-        <item x="663"/>
-        <item x="664"/>
-        <item x="665"/>
-        <item x="666"/>
-        <item x="667"/>
-        <item x="668"/>
-        <item x="66"/>
-        <item x="669"/>
-        <item x="670"/>
-        <item x="671"/>
-        <item x="672"/>
-        <item x="673"/>
-        <item x="674"/>
-        <item x="675"/>
-        <item x="676"/>
-        <item x="677"/>
-        <item x="678"/>
-        <item x="67"/>
-        <item x="679"/>
-        <item x="680"/>
-        <item x="681"/>
-        <item x="682"/>
-        <item x="683"/>
-        <item x="684"/>
-        <item x="685"/>
-        <item x="686"/>
-        <item x="687"/>
-        <item x="688"/>
-        <item x="68"/>
-        <item x="689"/>
-        <item x="690"/>
-        <item x="691"/>
-        <item x="692"/>
-        <item x="693"/>
-        <item x="694"/>
-        <item x="695"/>
-        <item x="696"/>
-        <item x="697"/>
-        <item x="698"/>
-        <item x="6"/>
-        <item x="69"/>
-        <item x="699"/>
-        <item x="700"/>
-        <item x="701"/>
-        <item x="702"/>
-        <item x="703"/>
-        <item x="704"/>
-        <item x="705"/>
-        <item x="706"/>
-        <item x="707"/>
-        <item x="708"/>
-        <item x="70"/>
-        <item x="709"/>
-        <item x="710"/>
-        <item x="711"/>
-        <item x="712"/>
-        <item x="713"/>
-        <item x="714"/>
-        <item x="715"/>
-        <item x="716"/>
-        <item x="717"/>
-        <item x="718"/>
-        <item x="71"/>
-        <item x="719"/>
-        <item x="720"/>
-        <item x="721"/>
-        <item x="722"/>
-        <item x="723"/>
-        <item x="724"/>
-        <item x="725"/>
-        <item x="726"/>
-        <item x="727"/>
-        <item x="728"/>
-        <item x="72"/>
-        <item x="729"/>
-        <item x="730"/>
-        <item x="731"/>
-        <item x="732"/>
-        <item x="733"/>
-        <item x="734"/>
-        <item x="735"/>
-        <item x="736"/>
-        <item x="737"/>
-        <item x="738"/>
-        <item x="73"/>
-        <item x="739"/>
-        <item x="740"/>
-        <item x="741"/>
-        <item x="742"/>
-        <item x="743"/>
-        <item x="744"/>
-        <item x="745"/>
-        <item x="746"/>
-        <item x="747"/>
-        <item x="748"/>
-        <item x="74"/>
-        <item x="749"/>
-        <item x="750"/>
-        <item x="751"/>
-        <item x="752"/>
-        <item x="753"/>
-        <item x="754"/>
-        <item x="755"/>
-        <item x="756"/>
-        <item x="757"/>
-        <item x="758"/>
-        <item x="75"/>
-        <item x="759"/>
-        <item x="760"/>
-        <item x="761"/>
-        <item x="762"/>
-        <item x="763"/>
-        <item x="764"/>
-        <item x="765"/>
-        <item x="766"/>
-        <item x="767"/>
-        <item x="768"/>
-        <item x="76"/>
-        <item x="769"/>
-        <item x="770"/>
-        <item x="771"/>
-        <item x="772"/>
-        <item x="773"/>
-        <item x="774"/>
-        <item x="775"/>
-        <item x="776"/>
-        <item x="777"/>
-        <item x="778"/>
-        <item x="77"/>
-        <item x="779"/>
-        <item x="780"/>
-        <item x="781"/>
-        <item x="782"/>
-        <item x="783"/>
-        <item x="784"/>
-        <item x="785"/>
-        <item x="786"/>
-        <item x="787"/>
-        <item x="788"/>
-        <item x="78"/>
-        <item x="789"/>
-        <item x="790"/>
-        <item x="791"/>
-        <item x="792"/>
-        <item x="793"/>
-        <item x="794"/>
-        <item x="795"/>
-        <item x="796"/>
-        <item x="797"/>
-        <item x="798"/>
-        <item x="7"/>
-        <item x="79"/>
-        <item x="799"/>
-        <item x="800"/>
-        <item x="801"/>
-        <item x="802"/>
-        <item x="803"/>
-        <item x="804"/>
-        <item x="805"/>
-        <item x="806"/>
-        <item x="807"/>
-        <item x="808"/>
-        <item x="80"/>
-        <item x="809"/>
-        <item x="810"/>
-        <item x="811"/>
-        <item x="812"/>
-        <item x="813"/>
-        <item x="814"/>
-        <item x="815"/>
-        <item x="816"/>
-        <item x="817"/>
-        <item x="818"/>
-        <item x="81"/>
-        <item x="819"/>
-        <item x="820"/>
-        <item x="821"/>
-        <item x="822"/>
-        <item x="823"/>
-        <item x="824"/>
-        <item x="825"/>
-        <item x="826"/>
-        <item x="827"/>
-        <item x="828"/>
-        <item x="82"/>
-        <item x="829"/>
-        <item x="830"/>
-        <item x="831"/>
-        <item x="832"/>
-        <item x="833"/>
-        <item x="834"/>
-        <item x="835"/>
-        <item x="836"/>
-        <item x="837"/>
-        <item x="838"/>
-        <item x="83"/>
-        <item x="839"/>
-        <item x="840"/>
-        <item x="841"/>
-        <item x="842"/>
-        <item x="843"/>
-        <item x="844"/>
-        <item x="845"/>
-        <item x="846"/>
-        <item x="847"/>
-        <item x="848"/>
-        <item x="84"/>
-        <item x="849"/>
-        <item x="850"/>
-        <item x="851"/>
-        <item x="852"/>
-        <item x="853"/>
-        <item x="854"/>
-        <item x="855"/>
-        <item x="856"/>
-        <item x="857"/>
-        <item x="858"/>
-        <item x="85"/>
-        <item x="859"/>
-        <item x="860"/>
-        <item x="861"/>
-        <item x="862"/>
-        <item x="863"/>
-        <item x="864"/>
-        <item x="865"/>
-        <item x="866"/>
-        <item x="867"/>
-        <item x="868"/>
-        <item x="86"/>
-        <item x="869"/>
-        <item x="870"/>
-        <item x="871"/>
-        <item x="872"/>
-        <item x="873"/>
-        <item x="874"/>
-        <item x="875"/>
-        <item x="876"/>
-        <item x="877"/>
-        <item x="878"/>
-        <item x="87"/>
-        <item x="879"/>
-        <item x="880"/>
-        <item x="881"/>
-        <item x="882"/>
-        <item x="883"/>
-        <item x="884"/>
-        <item x="885"/>
-        <item x="886"/>
-        <item x="887"/>
-        <item x="888"/>
-        <item x="88"/>
-        <item x="889"/>
-        <item x="890"/>
-        <item x="891"/>
-        <item x="892"/>
-        <item x="893"/>
-        <item x="894"/>
-        <item x="895"/>
-        <item x="896"/>
-        <item x="897"/>
-        <item x="898"/>
-        <item x="8"/>
-        <item x="89"/>
-        <item x="899"/>
-        <item x="900"/>
-        <item x="901"/>
-        <item x="902"/>
-        <item x="903"/>
-        <item x="904"/>
-        <item x="905"/>
-        <item x="906"/>
-        <item x="907"/>
-        <item x="908"/>
-        <item x="90"/>
-        <item x="909"/>
-        <item x="910"/>
-        <item x="911"/>
-        <item x="912"/>
-        <item x="913"/>
-        <item x="914"/>
-        <item x="915"/>
-        <item x="916"/>
-        <item x="917"/>
-        <item x="918"/>
-        <item x="91"/>
-        <item x="919"/>
-        <item x="920"/>
-        <item x="921"/>
-        <item x="922"/>
-        <item x="923"/>
-        <item x="924"/>
-        <item x="925"/>
-        <item x="926"/>
-        <item x="927"/>
-        <item x="928"/>
-        <item x="92"/>
-        <item x="929"/>
-        <item x="930"/>
-        <item x="931"/>
-        <item x="932"/>
-        <item x="933"/>
-        <item x="934"/>
-        <item x="935"/>
-        <item x="936"/>
-        <item x="937"/>
-        <item x="938"/>
-        <item x="93"/>
-        <item x="939"/>
-        <item x="940"/>
-        <item x="941"/>
-        <item x="942"/>
-        <item x="943"/>
-        <item x="944"/>
-        <item x="945"/>
-        <item x="946"/>
-        <item x="947"/>
-        <item x="948"/>
-        <item x="94"/>
-        <item x="949"/>
-        <item x="950"/>
-        <item x="951"/>
-        <item x="952"/>
-        <item x="953"/>
-        <item x="954"/>
-        <item x="955"/>
-        <item x="956"/>
-        <item x="957"/>
-        <item x="958"/>
-        <item x="95"/>
-        <item x="959"/>
-        <item x="960"/>
-        <item x="961"/>
-        <item x="962"/>
-        <item x="963"/>
-        <item x="964"/>
-        <item x="965"/>
-        <item x="966"/>
-        <item x="967"/>
-        <item x="968"/>
-        <item x="96"/>
-        <item x="969"/>
-        <item x="970"/>
-        <item x="971"/>
-        <item x="972"/>
-        <item x="973"/>
-        <item x="974"/>
-        <item x="975"/>
-        <item x="976"/>
-        <item x="977"/>
-        <item x="978"/>
-        <item x="97"/>
-        <item x="979"/>
-        <item x="980"/>
-        <item x="981"/>
-        <item x="982"/>
-        <item x="983"/>
-        <item x="984"/>
-        <item x="985"/>
-        <item x="986"/>
-        <item x="987"/>
-        <item x="988"/>
-        <item x="98"/>
-        <item x="989"/>
-        <item x="990"/>
-        <item x="991"/>
-        <item x="992"/>
-        <item x="993"/>
-        <item x="994"/>
-        <item x="995"/>
-        <item x="996"/>
-        <item x="997"/>
-        <item x="998"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="32">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="8"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order_Id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="63">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="62">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="61">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="60">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="59">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="58">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="3">
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="21" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{030ED229-A10E-49DC-B1D7-4E2AE8584D8E}" name="PivotTable9" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
-  <location ref="A82:B88" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField showAll="0">
-      <items count="1301">
-        <item x="0"/>
-        <item x="9"/>
-        <item x="99"/>
-        <item x="999"/>
-        <item x="1000"/>
-        <item x="1001"/>
-        <item x="1002"/>
-        <item x="1003"/>
-        <item x="1004"/>
-        <item x="1005"/>
-        <item x="1006"/>
-        <item x="1007"/>
-        <item x="1008"/>
-        <item x="100"/>
-        <item x="1009"/>
-        <item x="1010"/>
-        <item x="1011"/>
-        <item x="1012"/>
-        <item x="1013"/>
-        <item x="1014"/>
-        <item x="1015"/>
-        <item x="1016"/>
-        <item x="1017"/>
-        <item x="1018"/>
-        <item x="101"/>
-        <item x="1019"/>
-        <item x="1020"/>
-        <item x="1021"/>
-        <item x="1022"/>
-        <item x="1023"/>
-        <item x="1024"/>
-        <item x="1025"/>
-        <item x="1026"/>
-        <item x="1027"/>
-        <item x="1028"/>
-        <item x="102"/>
-        <item x="1029"/>
-        <item x="1030"/>
-        <item x="1031"/>
-        <item x="1032"/>
-        <item x="1033"/>
-        <item x="1034"/>
-        <item x="1035"/>
-        <item x="1036"/>
-        <item x="1037"/>
-        <item x="1038"/>
-        <item x="103"/>
-        <item x="1039"/>
-        <item x="1040"/>
-        <item x="1041"/>
-        <item x="1042"/>
-        <item x="1043"/>
-        <item x="1044"/>
-        <item x="1045"/>
-        <item x="1046"/>
-        <item x="1047"/>
-        <item x="1048"/>
-        <item x="104"/>
-        <item x="1049"/>
-        <item x="1050"/>
-        <item x="1051"/>
-        <item x="1052"/>
-        <item x="1053"/>
-        <item x="1054"/>
-        <item x="1055"/>
-        <item x="1056"/>
-        <item x="1057"/>
-        <item x="1058"/>
-        <item x="105"/>
-        <item x="1059"/>
-        <item x="1060"/>
-        <item x="1061"/>
-        <item x="1062"/>
-        <item x="1063"/>
-        <item x="1064"/>
-        <item x="1065"/>
-        <item x="1066"/>
-        <item x="1067"/>
-        <item x="1068"/>
-        <item x="106"/>
-        <item x="1069"/>
-        <item x="1070"/>
-        <item x="1071"/>
-        <item x="1072"/>
-        <item x="1073"/>
-        <item x="1074"/>
-        <item x="1075"/>
-        <item x="1076"/>
-        <item x="1077"/>
-        <item x="1078"/>
-        <item x="107"/>
-        <item x="1079"/>
-        <item x="1080"/>
-        <item x="1081"/>
-        <item x="1082"/>
-        <item x="1083"/>
-        <item x="1084"/>
-        <item x="1085"/>
-        <item x="1086"/>
-        <item x="1087"/>
-        <item x="1088"/>
-        <item x="108"/>
-        <item x="1089"/>
-        <item x="1090"/>
-        <item x="1091"/>
-        <item x="1092"/>
-        <item x="1093"/>
-        <item x="1094"/>
-        <item x="1095"/>
-        <item x="1096"/>
-        <item x="1097"/>
-        <item x="1098"/>
-        <item x="10"/>
-        <item x="109"/>
-        <item x="1099"/>
-        <item x="1100"/>
-        <item x="1101"/>
-        <item x="1102"/>
-        <item x="1103"/>
-        <item x="1104"/>
-        <item x="1105"/>
-        <item x="1106"/>
-        <item x="1107"/>
-        <item x="1108"/>
-        <item x="110"/>
-        <item x="1109"/>
-        <item x="1110"/>
-        <item x="1111"/>
-        <item x="1112"/>
-        <item x="1113"/>
-        <item x="1114"/>
-        <item x="1115"/>
-        <item x="1116"/>
-        <item x="1117"/>
-        <item x="1118"/>
-        <item x="111"/>
-        <item x="1119"/>
-        <item x="1120"/>
-        <item x="1121"/>
-        <item x="1122"/>
-        <item x="1123"/>
-        <item x="1124"/>
-        <item x="1125"/>
-        <item x="1126"/>
-        <item x="1127"/>
-        <item x="1128"/>
-        <item x="112"/>
-        <item x="1129"/>
-        <item x="1130"/>
-        <item x="1131"/>
-        <item x="1132"/>
-        <item x="1133"/>
-        <item x="1134"/>
-        <item x="1135"/>
-        <item x="1136"/>
-        <item x="1137"/>
-        <item x="1138"/>
-        <item x="113"/>
-        <item x="1139"/>
-        <item x="1140"/>
-        <item x="1141"/>
-        <item x="1142"/>
-        <item x="1143"/>
-        <item x="1144"/>
-        <item x="1145"/>
-        <item x="1146"/>
-        <item x="1147"/>
-        <item x="1148"/>
-        <item x="114"/>
-        <item x="1149"/>
-        <item x="1150"/>
-        <item x="1151"/>
-        <item x="1152"/>
-        <item x="1153"/>
-        <item x="1154"/>
-        <item x="1155"/>
-        <item x="1156"/>
-        <item x="1157"/>
-        <item x="1158"/>
-        <item x="115"/>
-        <item x="1159"/>
-        <item x="1160"/>
-        <item x="1161"/>
-        <item x="1162"/>
-        <item x="1163"/>
-        <item x="1164"/>
-        <item x="1165"/>
-        <item x="1166"/>
-        <item x="1167"/>
-        <item x="1168"/>
-        <item x="116"/>
-        <item x="1169"/>
-        <item x="1170"/>
-        <item x="1171"/>
-        <item x="1172"/>
-        <item x="1173"/>
-        <item x="1174"/>
-        <item x="1175"/>
-        <item x="1176"/>
-        <item x="1177"/>
-        <item x="1178"/>
-        <item x="117"/>
-        <item x="1179"/>
-        <item x="1180"/>
-        <item x="1181"/>
-        <item x="1182"/>
-        <item x="1183"/>
-        <item x="1184"/>
-        <item x="1185"/>
-        <item x="1186"/>
-        <item x="1187"/>
-        <item x="1188"/>
-        <item x="118"/>
-        <item x="1189"/>
-        <item x="1190"/>
-        <item x="1191"/>
-        <item x="1192"/>
-        <item x="1193"/>
-        <item x="1194"/>
-        <item x="1195"/>
-        <item x="1196"/>
-        <item x="1197"/>
-        <item x="1198"/>
-        <item x="11"/>
-        <item x="119"/>
-        <item x="1199"/>
-        <item x="1200"/>
-        <item x="1201"/>
-        <item x="1202"/>
-        <item x="1203"/>
-        <item x="1204"/>
-        <item x="1205"/>
-        <item x="1206"/>
-        <item x="1207"/>
-        <item x="1208"/>
-        <item x="120"/>
-        <item x="1209"/>
-        <item x="1210"/>
-        <item x="1211"/>
-        <item x="1212"/>
-        <item x="1213"/>
-        <item x="1214"/>
-        <item x="1215"/>
-        <item x="1216"/>
-        <item x="1217"/>
-        <item x="1218"/>
-        <item x="121"/>
-        <item x="1219"/>
-        <item x="1220"/>
-        <item x="1221"/>
-        <item x="1222"/>
-        <item x="1223"/>
-        <item x="1224"/>
-        <item x="1225"/>
-        <item x="1226"/>
-        <item x="1227"/>
-        <item x="1228"/>
-        <item x="122"/>
-        <item x="1229"/>
-        <item x="1230"/>
-        <item x="1231"/>
-        <item x="1232"/>
-        <item x="1233"/>
-        <item x="1234"/>
-        <item x="1235"/>
-        <item x="1236"/>
-        <item x="1237"/>
-        <item x="1238"/>
-        <item x="123"/>
-        <item x="1239"/>
-        <item x="1240"/>
-        <item x="1241"/>
-        <item x="1242"/>
-        <item x="1243"/>
-        <item x="1244"/>
-        <item x="1245"/>
-        <item x="1246"/>
-        <item x="1247"/>
-        <item x="1248"/>
-        <item x="124"/>
-        <item x="1249"/>
-        <item x="1250"/>
-        <item x="1251"/>
-        <item x="1252"/>
-        <item x="1253"/>
-        <item x="1254"/>
-        <item x="1255"/>
-        <item x="1256"/>
-        <item x="1257"/>
-        <item x="1258"/>
-        <item x="125"/>
-        <item x="1259"/>
-        <item x="1260"/>
-        <item x="1261"/>
-        <item x="1262"/>
-        <item x="1263"/>
-        <item x="1264"/>
-        <item x="1265"/>
-        <item x="1266"/>
-        <item x="1267"/>
-        <item x="1268"/>
-        <item x="126"/>
-        <item x="1269"/>
-        <item x="1270"/>
-        <item x="1271"/>
-        <item x="1272"/>
-        <item x="1273"/>
-        <item x="1274"/>
-        <item x="1275"/>
-        <item x="1276"/>
-        <item x="1277"/>
-        <item x="1278"/>
-        <item x="127"/>
-        <item x="1279"/>
-        <item x="1280"/>
-        <item x="1281"/>
-        <item x="1282"/>
-        <item x="1283"/>
-        <item x="1284"/>
-        <item x="1285"/>
-        <item x="1286"/>
-        <item x="1287"/>
-        <item x="1288"/>
-        <item x="128"/>
-        <item x="1289"/>
-        <item x="1290"/>
-        <item x="1291"/>
-        <item x="1292"/>
-        <item x="1293"/>
-        <item x="1294"/>
-        <item x="1295"/>
-        <item x="1296"/>
-        <item x="1297"/>
-        <item x="1298"/>
-        <item x="12"/>
-        <item x="129"/>
-        <item x="1299"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="13"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="14"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="15"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="16"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="17"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="18"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="20"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="21"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="22"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="23"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="24"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="25"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="26"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="27"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="28"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="30"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="31"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="32"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="33"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="34"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="35"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item x="368"/>
-        <item x="36"/>
-        <item x="369"/>
-        <item x="370"/>
-        <item x="371"/>
-        <item x="372"/>
-        <item x="373"/>
-        <item x="374"/>
-        <item x="375"/>
-        <item x="376"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="37"/>
-        <item x="379"/>
-        <item x="380"/>
-        <item x="381"/>
-        <item x="382"/>
-        <item x="383"/>
-        <item x="384"/>
-        <item x="385"/>
-        <item x="386"/>
-        <item x="387"/>
-        <item x="388"/>
-        <item x="38"/>
-        <item x="389"/>
-        <item x="390"/>
-        <item x="391"/>
-        <item x="392"/>
-        <item x="393"/>
-        <item x="394"/>
-        <item x="395"/>
-        <item x="396"/>
-        <item x="397"/>
-        <item x="398"/>
-        <item x="3"/>
-        <item x="39"/>
-        <item x="399"/>
-        <item x="400"/>
-        <item x="401"/>
-        <item x="402"/>
-        <item x="403"/>
-        <item x="404"/>
-        <item x="405"/>
-        <item x="406"/>
-        <item x="407"/>
-        <item x="408"/>
-        <item x="40"/>
-        <item x="409"/>
-        <item x="410"/>
-        <item x="411"/>
-        <item x="412"/>
-        <item x="413"/>
-        <item x="414"/>
-        <item x="415"/>
-        <item x="416"/>
-        <item x="417"/>
-        <item x="418"/>
-        <item x="41"/>
-        <item x="419"/>
-        <item x="420"/>
-        <item x="421"/>
-        <item x="422"/>
-        <item x="423"/>
-        <item x="424"/>
-        <item x="425"/>
-        <item x="426"/>
-        <item x="427"/>
-        <item x="428"/>
-        <item x="42"/>
-        <item x="429"/>
-        <item x="430"/>
-        <item x="431"/>
-        <item x="432"/>
-        <item x="433"/>
-        <item x="434"/>
-        <item x="435"/>
-        <item x="436"/>
-        <item x="437"/>
-        <item x="438"/>
-        <item x="43"/>
-        <item x="439"/>
-        <item x="440"/>
-        <item x="441"/>
-        <item x="442"/>
-        <item x="443"/>
-        <item x="444"/>
-        <item x="445"/>
-        <item x="446"/>
-        <item x="447"/>
-        <item x="448"/>
-        <item x="44"/>
-        <item x="449"/>
-        <item x="450"/>
-        <item x="451"/>
-        <item x="452"/>
-        <item x="453"/>
-        <item x="454"/>
-        <item x="455"/>
-        <item x="456"/>
-        <item x="457"/>
-        <item x="458"/>
-        <item x="45"/>
-        <item x="459"/>
-        <item x="460"/>
-        <item x="461"/>
-        <item x="462"/>
-        <item x="463"/>
-        <item x="464"/>
-        <item x="465"/>
-        <item x="466"/>
-        <item x="467"/>
-        <item x="468"/>
-        <item x="46"/>
-        <item x="469"/>
-        <item x="470"/>
-        <item x="471"/>
-        <item x="472"/>
-        <item x="473"/>
-        <item x="474"/>
-        <item x="475"/>
-        <item x="476"/>
-        <item x="477"/>
-        <item x="478"/>
-        <item x="47"/>
-        <item x="479"/>
-        <item x="480"/>
-        <item x="481"/>
-        <item x="482"/>
-        <item x="483"/>
-        <item x="484"/>
-        <item x="485"/>
-        <item x="486"/>
-        <item x="487"/>
-        <item x="488"/>
-        <item x="48"/>
-        <item x="489"/>
-        <item x="490"/>
-        <item x="491"/>
-        <item x="492"/>
-        <item x="493"/>
-        <item x="494"/>
-        <item x="495"/>
-        <item x="496"/>
-        <item x="497"/>
-        <item x="498"/>
-        <item x="4"/>
-        <item x="49"/>
-        <item x="499"/>
-        <item x="500"/>
-        <item x="501"/>
-        <item x="502"/>
-        <item x="503"/>
-        <item x="504"/>
-        <item x="505"/>
-        <item x="506"/>
-        <item x="507"/>
-        <item x="508"/>
-        <item x="50"/>
-        <item x="509"/>
-        <item x="510"/>
-        <item x="511"/>
-        <item x="512"/>
-        <item x="513"/>
-        <item x="514"/>
-        <item x="515"/>
-        <item x="516"/>
-        <item x="517"/>
-        <item x="518"/>
-        <item x="51"/>
-        <item x="519"/>
-        <item x="520"/>
-        <item x="521"/>
-        <item x="522"/>
-        <item x="523"/>
-        <item x="524"/>
-        <item x="525"/>
-        <item x="526"/>
-        <item x="527"/>
-        <item x="528"/>
-        <item x="52"/>
-        <item x="529"/>
-        <item x="530"/>
-        <item x="531"/>
-        <item x="532"/>
-        <item x="533"/>
-        <item x="534"/>
-        <item x="535"/>
-        <item x="536"/>
-        <item x="537"/>
-        <item x="538"/>
-        <item x="53"/>
-        <item x="539"/>
-        <item x="540"/>
-        <item x="541"/>
-        <item x="542"/>
-        <item x="543"/>
-        <item x="544"/>
-        <item x="545"/>
-        <item x="546"/>
-        <item x="547"/>
-        <item x="548"/>
-        <item x="54"/>
-        <item x="549"/>
-        <item x="550"/>
-        <item x="551"/>
-        <item x="552"/>
-        <item x="553"/>
-        <item x="554"/>
-        <item x="555"/>
-        <item x="556"/>
-        <item x="557"/>
-        <item x="558"/>
-        <item x="55"/>
-        <item x="559"/>
-        <item x="560"/>
-        <item x="561"/>
-        <item x="562"/>
-        <item x="563"/>
-        <item x="564"/>
-        <item x="565"/>
-        <item x="566"/>
-        <item x="567"/>
-        <item x="568"/>
-        <item x="56"/>
-        <item x="569"/>
-        <item x="570"/>
-        <item x="571"/>
-        <item x="572"/>
-        <item x="573"/>
-        <item x="574"/>
-        <item x="575"/>
-        <item x="576"/>
-        <item x="577"/>
-        <item x="578"/>
-        <item x="57"/>
-        <item x="579"/>
-        <item x="580"/>
-        <item x="581"/>
-        <item x="582"/>
-        <item x="583"/>
-        <item x="584"/>
-        <item x="585"/>
-        <item x="586"/>
-        <item x="587"/>
-        <item x="588"/>
-        <item x="58"/>
-        <item x="589"/>
-        <item x="590"/>
-        <item x="591"/>
-        <item x="592"/>
-        <item x="593"/>
-        <item x="594"/>
-        <item x="595"/>
-        <item x="596"/>
-        <item x="597"/>
-        <item x="598"/>
-        <item x="5"/>
-        <item x="59"/>
-        <item x="599"/>
-        <item x="600"/>
-        <item x="601"/>
-        <item x="602"/>
-        <item x="603"/>
-        <item x="604"/>
-        <item x="605"/>
-        <item x="606"/>
-        <item x="607"/>
-        <item x="608"/>
-        <item x="60"/>
-        <item x="609"/>
-        <item x="610"/>
-        <item x="611"/>
-        <item x="612"/>
-        <item x="613"/>
-        <item x="614"/>
-        <item x="615"/>
-        <item x="616"/>
-        <item x="617"/>
-        <item x="618"/>
-        <item x="61"/>
-        <item x="619"/>
-        <item x="620"/>
-        <item x="621"/>
-        <item x="622"/>
-        <item x="623"/>
-        <item x="624"/>
-        <item x="625"/>
-        <item x="626"/>
-        <item x="627"/>
-        <item x="628"/>
-        <item x="62"/>
-        <item x="629"/>
-        <item x="630"/>
-        <item x="631"/>
-        <item x="632"/>
-        <item x="633"/>
-        <item x="634"/>
-        <item x="635"/>
-        <item x="636"/>
-        <item x="637"/>
-        <item x="638"/>
-        <item x="63"/>
-        <item x="639"/>
-        <item x="640"/>
-        <item x="641"/>
-        <item x="642"/>
-        <item x="643"/>
-        <item x="644"/>
-        <item x="645"/>
-        <item x="646"/>
-        <item x="647"/>
-        <item x="648"/>
-        <item x="64"/>
-        <item x="649"/>
-        <item x="650"/>
-        <item x="651"/>
-        <item x="652"/>
-        <item x="653"/>
-        <item x="654"/>
-        <item x="655"/>
-        <item x="656"/>
-        <item x="657"/>
-        <item x="658"/>
-        <item x="65"/>
-        <item x="659"/>
-        <item x="660"/>
-        <item x="661"/>
-        <item x="662"/>
-        <item x="663"/>
-        <item x="664"/>
-        <item x="665"/>
-        <item x="666"/>
-        <item x="667"/>
-        <item x="668"/>
-        <item x="66"/>
-        <item x="669"/>
-        <item x="670"/>
-        <item x="671"/>
-        <item x="672"/>
-        <item x="673"/>
-        <item x="674"/>
-        <item x="675"/>
-        <item x="676"/>
-        <item x="677"/>
-        <item x="678"/>
-        <item x="67"/>
-        <item x="679"/>
-        <item x="680"/>
-        <item x="681"/>
-        <item x="682"/>
-        <item x="683"/>
-        <item x="684"/>
-        <item x="685"/>
-        <item x="686"/>
-        <item x="687"/>
-        <item x="688"/>
-        <item x="68"/>
-        <item x="689"/>
-        <item x="690"/>
-        <item x="691"/>
-        <item x="692"/>
-        <item x="693"/>
-        <item x="694"/>
-        <item x="695"/>
-        <item x="696"/>
-        <item x="697"/>
-        <item x="698"/>
-        <item x="6"/>
-        <item x="69"/>
-        <item x="699"/>
-        <item x="700"/>
-        <item x="701"/>
-        <item x="702"/>
-        <item x="703"/>
-        <item x="704"/>
-        <item x="705"/>
-        <item x="706"/>
-        <item x="707"/>
-        <item x="708"/>
-        <item x="70"/>
-        <item x="709"/>
-        <item x="710"/>
-        <item x="711"/>
-        <item x="712"/>
-        <item x="713"/>
-        <item x="714"/>
-        <item x="715"/>
-        <item x="716"/>
-        <item x="717"/>
-        <item x="718"/>
-        <item x="71"/>
-        <item x="719"/>
-        <item x="720"/>
-        <item x="721"/>
-        <item x="722"/>
-        <item x="723"/>
-        <item x="724"/>
-        <item x="725"/>
-        <item x="726"/>
-        <item x="727"/>
-        <item x="728"/>
-        <item x="72"/>
-        <item x="729"/>
-        <item x="730"/>
-        <item x="731"/>
-        <item x="732"/>
-        <item x="733"/>
-        <item x="734"/>
-        <item x="735"/>
-        <item x="736"/>
-        <item x="737"/>
-        <item x="738"/>
-        <item x="73"/>
-        <item x="739"/>
-        <item x="740"/>
-        <item x="741"/>
-        <item x="742"/>
-        <item x="743"/>
-        <item x="744"/>
-        <item x="745"/>
-        <item x="746"/>
-        <item x="747"/>
-        <item x="748"/>
-        <item x="74"/>
-        <item x="749"/>
-        <item x="750"/>
-        <item x="751"/>
-        <item x="752"/>
-        <item x="753"/>
-        <item x="754"/>
-        <item x="755"/>
-        <item x="756"/>
-        <item x="757"/>
-        <item x="758"/>
-        <item x="75"/>
-        <item x="759"/>
-        <item x="760"/>
-        <item x="761"/>
-        <item x="762"/>
-        <item x="763"/>
-        <item x="764"/>
-        <item x="765"/>
-        <item x="766"/>
-        <item x="767"/>
-        <item x="768"/>
-        <item x="76"/>
-        <item x="769"/>
-        <item x="770"/>
-        <item x="771"/>
-        <item x="772"/>
-        <item x="773"/>
-        <item x="774"/>
-        <item x="775"/>
-        <item x="776"/>
-        <item x="777"/>
-        <item x="778"/>
-        <item x="77"/>
-        <item x="779"/>
-        <item x="780"/>
-        <item x="781"/>
-        <item x="782"/>
-        <item x="783"/>
-        <item x="784"/>
-        <item x="785"/>
-        <item x="786"/>
-        <item x="787"/>
-        <item x="788"/>
-        <item x="78"/>
-        <item x="789"/>
-        <item x="790"/>
-        <item x="791"/>
-        <item x="792"/>
-        <item x="793"/>
-        <item x="794"/>
-        <item x="795"/>
-        <item x="796"/>
-        <item x="797"/>
-        <item x="798"/>
-        <item x="7"/>
-        <item x="79"/>
-        <item x="799"/>
-        <item x="800"/>
-        <item x="801"/>
-        <item x="802"/>
-        <item x="803"/>
-        <item x="804"/>
-        <item x="805"/>
-        <item x="806"/>
-        <item x="807"/>
-        <item x="808"/>
-        <item x="80"/>
-        <item x="809"/>
-        <item x="810"/>
-        <item x="811"/>
-        <item x="812"/>
-        <item x="813"/>
-        <item x="814"/>
-        <item x="815"/>
-        <item x="816"/>
-        <item x="817"/>
-        <item x="818"/>
-        <item x="81"/>
-        <item x="819"/>
-        <item x="820"/>
-        <item x="821"/>
-        <item x="822"/>
-        <item x="823"/>
-        <item x="824"/>
-        <item x="825"/>
-        <item x="826"/>
-        <item x="827"/>
-        <item x="828"/>
-        <item x="82"/>
-        <item x="829"/>
-        <item x="830"/>
-        <item x="831"/>
-        <item x="832"/>
-        <item x="833"/>
-        <item x="834"/>
-        <item x="835"/>
-        <item x="836"/>
-        <item x="837"/>
-        <item x="838"/>
-        <item x="83"/>
-        <item x="839"/>
-        <item x="840"/>
-        <item x="841"/>
-        <item x="842"/>
-        <item x="843"/>
-        <item x="844"/>
-        <item x="845"/>
-        <item x="846"/>
-        <item x="847"/>
-        <item x="848"/>
-        <item x="84"/>
-        <item x="849"/>
-        <item x="850"/>
-        <item x="851"/>
-        <item x="852"/>
-        <item x="853"/>
-        <item x="854"/>
-        <item x="855"/>
-        <item x="856"/>
-        <item x="857"/>
-        <item x="858"/>
-        <item x="85"/>
-        <item x="859"/>
-        <item x="860"/>
-        <item x="861"/>
-        <item x="862"/>
-        <item x="863"/>
-        <item x="864"/>
-        <item x="865"/>
-        <item x="866"/>
-        <item x="867"/>
-        <item x="868"/>
-        <item x="86"/>
-        <item x="869"/>
-        <item x="870"/>
-        <item x="871"/>
-        <item x="872"/>
-        <item x="873"/>
-        <item x="874"/>
-        <item x="875"/>
-        <item x="876"/>
-        <item x="877"/>
-        <item x="878"/>
-        <item x="87"/>
-        <item x="879"/>
-        <item x="880"/>
-        <item x="881"/>
-        <item x="882"/>
-        <item x="883"/>
-        <item x="884"/>
-        <item x="885"/>
-        <item x="886"/>
-        <item x="887"/>
-        <item x="888"/>
-        <item x="88"/>
-        <item x="889"/>
-        <item x="890"/>
-        <item x="891"/>
-        <item x="892"/>
-        <item x="893"/>
-        <item x="894"/>
-        <item x="895"/>
-        <item x="896"/>
-        <item x="897"/>
-        <item x="898"/>
-        <item x="8"/>
-        <item x="89"/>
-        <item x="899"/>
-        <item x="900"/>
-        <item x="901"/>
-        <item x="902"/>
-        <item x="903"/>
-        <item x="904"/>
-        <item x="905"/>
-        <item x="906"/>
-        <item x="907"/>
-        <item x="908"/>
-        <item x="90"/>
-        <item x="909"/>
-        <item x="910"/>
-        <item x="911"/>
-        <item x="912"/>
-        <item x="913"/>
-        <item x="914"/>
-        <item x="915"/>
-        <item x="916"/>
-        <item x="917"/>
-        <item x="918"/>
-        <item x="91"/>
-        <item x="919"/>
-        <item x="920"/>
-        <item x="921"/>
-        <item x="922"/>
-        <item x="923"/>
-        <item x="924"/>
-        <item x="925"/>
-        <item x="926"/>
-        <item x="927"/>
-        <item x="928"/>
-        <item x="92"/>
-        <item x="929"/>
-        <item x="930"/>
-        <item x="931"/>
-        <item x="932"/>
-        <item x="933"/>
-        <item x="934"/>
-        <item x="935"/>
-        <item x="936"/>
-        <item x="937"/>
-        <item x="938"/>
-        <item x="93"/>
-        <item x="939"/>
-        <item x="940"/>
-        <item x="941"/>
-        <item x="942"/>
-        <item x="943"/>
-        <item x="944"/>
-        <item x="945"/>
-        <item x="946"/>
-        <item x="947"/>
-        <item x="948"/>
-        <item x="94"/>
-        <item x="949"/>
-        <item x="950"/>
-        <item x="951"/>
-        <item x="952"/>
-        <item x="953"/>
-        <item x="954"/>
-        <item x="955"/>
-        <item x="956"/>
-        <item x="957"/>
-        <item x="958"/>
-        <item x="95"/>
-        <item x="959"/>
-        <item x="960"/>
-        <item x="961"/>
-        <item x="962"/>
-        <item x="963"/>
-        <item x="964"/>
-        <item x="965"/>
-        <item x="966"/>
-        <item x="967"/>
-        <item x="968"/>
-        <item x="96"/>
-        <item x="969"/>
-        <item x="970"/>
-        <item x="971"/>
-        <item x="972"/>
-        <item x="973"/>
-        <item x="974"/>
-        <item x="975"/>
-        <item x="976"/>
-        <item x="977"/>
-        <item x="978"/>
-        <item x="97"/>
-        <item x="979"/>
-        <item x="980"/>
-        <item x="981"/>
-        <item x="982"/>
-        <item x="983"/>
-        <item x="984"/>
-        <item x="985"/>
-        <item x="986"/>
-        <item x="987"/>
-        <item x="988"/>
-        <item x="98"/>
-        <item x="989"/>
-        <item x="990"/>
-        <item x="991"/>
-        <item x="992"/>
-        <item x="993"/>
-        <item x="994"/>
-        <item x="995"/>
-        <item x="996"/>
-        <item x="997"/>
-        <item x="998"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="32">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total commission" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="69">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="68">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="67">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="66">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="65">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="13" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68D9E7EF-3B4D-4F92-A5BE-1179E186F699}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="10">
-    <pivotField showAll="0">
-      <items count="1301">
-        <item x="0"/>
-        <item x="9"/>
-        <item x="99"/>
-        <item x="999"/>
-        <item x="1000"/>
-        <item x="1001"/>
-        <item x="1002"/>
-        <item x="1003"/>
-        <item x="1004"/>
-        <item x="1005"/>
-        <item x="1006"/>
-        <item x="1007"/>
-        <item x="1008"/>
-        <item x="100"/>
-        <item x="1009"/>
-        <item x="1010"/>
-        <item x="1011"/>
-        <item x="1012"/>
-        <item x="1013"/>
-        <item x="1014"/>
-        <item x="1015"/>
-        <item x="1016"/>
-        <item x="1017"/>
-        <item x="1018"/>
-        <item x="101"/>
-        <item x="1019"/>
-        <item x="1020"/>
-        <item x="1021"/>
-        <item x="1022"/>
-        <item x="1023"/>
-        <item x="1024"/>
-        <item x="1025"/>
-        <item x="1026"/>
-        <item x="1027"/>
-        <item x="1028"/>
-        <item x="102"/>
-        <item x="1029"/>
-        <item x="1030"/>
-        <item x="1031"/>
-        <item x="1032"/>
-        <item x="1033"/>
-        <item x="1034"/>
-        <item x="1035"/>
-        <item x="1036"/>
-        <item x="1037"/>
-        <item x="1038"/>
-        <item x="103"/>
-        <item x="1039"/>
-        <item x="1040"/>
-        <item x="1041"/>
-        <item x="1042"/>
-        <item x="1043"/>
-        <item x="1044"/>
-        <item x="1045"/>
-        <item x="1046"/>
-        <item x="1047"/>
-        <item x="1048"/>
-        <item x="104"/>
-        <item x="1049"/>
-        <item x="1050"/>
-        <item x="1051"/>
-        <item x="1052"/>
-        <item x="1053"/>
-        <item x="1054"/>
-        <item x="1055"/>
-        <item x="1056"/>
-        <item x="1057"/>
-        <item x="1058"/>
-        <item x="105"/>
-        <item x="1059"/>
-        <item x="1060"/>
-        <item x="1061"/>
-        <item x="1062"/>
-        <item x="1063"/>
-        <item x="1064"/>
-        <item x="1065"/>
-        <item x="1066"/>
-        <item x="1067"/>
-        <item x="1068"/>
-        <item x="106"/>
-        <item x="1069"/>
-        <item x="1070"/>
-        <item x="1071"/>
-        <item x="1072"/>
-        <item x="1073"/>
-        <item x="1074"/>
-        <item x="1075"/>
-        <item x="1076"/>
-        <item x="1077"/>
-        <item x="1078"/>
-        <item x="107"/>
-        <item x="1079"/>
-        <item x="1080"/>
-        <item x="1081"/>
-        <item x="1082"/>
-        <item x="1083"/>
-        <item x="1084"/>
-        <item x="1085"/>
-        <item x="1086"/>
-        <item x="1087"/>
-        <item x="1088"/>
-        <item x="108"/>
-        <item x="1089"/>
-        <item x="1090"/>
-        <item x="1091"/>
-        <item x="1092"/>
-        <item x="1093"/>
-        <item x="1094"/>
-        <item x="1095"/>
-        <item x="1096"/>
-        <item x="1097"/>
-        <item x="1098"/>
-        <item x="10"/>
-        <item x="109"/>
-        <item x="1099"/>
-        <item x="1100"/>
-        <item x="1101"/>
-        <item x="1102"/>
-        <item x="1103"/>
-        <item x="1104"/>
-        <item x="1105"/>
-        <item x="1106"/>
-        <item x="1107"/>
-        <item x="1108"/>
-        <item x="110"/>
-        <item x="1109"/>
-        <item x="1110"/>
-        <item x="1111"/>
-        <item x="1112"/>
-        <item x="1113"/>
-        <item x="1114"/>
-        <item x="1115"/>
-        <item x="1116"/>
-        <item x="1117"/>
-        <item x="1118"/>
-        <item x="111"/>
-        <item x="1119"/>
-        <item x="1120"/>
-        <item x="1121"/>
-        <item x="1122"/>
-        <item x="1123"/>
-        <item x="1124"/>
-        <item x="1125"/>
-        <item x="1126"/>
-        <item x="1127"/>
-        <item x="1128"/>
-        <item x="112"/>
-        <item x="1129"/>
-        <item x="1130"/>
-        <item x="1131"/>
-        <item x="1132"/>
-        <item x="1133"/>
-        <item x="1134"/>
-        <item x="1135"/>
-        <item x="1136"/>
-        <item x="1137"/>
-        <item x="1138"/>
-        <item x="113"/>
-        <item x="1139"/>
-        <item x="1140"/>
-        <item x="1141"/>
-        <item x="1142"/>
-        <item x="1143"/>
-        <item x="1144"/>
-        <item x="1145"/>
-        <item x="1146"/>
-        <item x="1147"/>
-        <item x="1148"/>
-        <item x="114"/>
-        <item x="1149"/>
-        <item x="1150"/>
-        <item x="1151"/>
-        <item x="1152"/>
-        <item x="1153"/>
-        <item x="1154"/>
-        <item x="1155"/>
-        <item x="1156"/>
-        <item x="1157"/>
-        <item x="1158"/>
-        <item x="115"/>
-        <item x="1159"/>
-        <item x="1160"/>
-        <item x="1161"/>
-        <item x="1162"/>
-        <item x="1163"/>
-        <item x="1164"/>
-        <item x="1165"/>
-        <item x="1166"/>
-        <item x="1167"/>
-        <item x="1168"/>
-        <item x="116"/>
-        <item x="1169"/>
-        <item x="1170"/>
-        <item x="1171"/>
-        <item x="1172"/>
-        <item x="1173"/>
-        <item x="1174"/>
-        <item x="1175"/>
-        <item x="1176"/>
-        <item x="1177"/>
-        <item x="1178"/>
-        <item x="117"/>
-        <item x="1179"/>
-        <item x="1180"/>
-        <item x="1181"/>
-        <item x="1182"/>
-        <item x="1183"/>
-        <item x="1184"/>
-        <item x="1185"/>
-        <item x="1186"/>
-        <item x="1187"/>
-        <item x="1188"/>
-        <item x="118"/>
-        <item x="1189"/>
-        <item x="1190"/>
-        <item x="1191"/>
-        <item x="1192"/>
-        <item x="1193"/>
-        <item x="1194"/>
-        <item x="1195"/>
-        <item x="1196"/>
-        <item x="1197"/>
-        <item x="1198"/>
-        <item x="11"/>
-        <item x="119"/>
-        <item x="1199"/>
-        <item x="1200"/>
-        <item x="1201"/>
-        <item x="1202"/>
-        <item x="1203"/>
-        <item x="1204"/>
-        <item x="1205"/>
-        <item x="1206"/>
-        <item x="1207"/>
-        <item x="1208"/>
-        <item x="120"/>
-        <item x="1209"/>
-        <item x="1210"/>
-        <item x="1211"/>
-        <item x="1212"/>
-        <item x="1213"/>
-        <item x="1214"/>
-        <item x="1215"/>
-        <item x="1216"/>
-        <item x="1217"/>
-        <item x="1218"/>
-        <item x="121"/>
-        <item x="1219"/>
-        <item x="1220"/>
-        <item x="1221"/>
-        <item x="1222"/>
-        <item x="1223"/>
-        <item x="1224"/>
-        <item x="1225"/>
-        <item x="1226"/>
-        <item x="1227"/>
-        <item x="1228"/>
-        <item x="122"/>
-        <item x="1229"/>
-        <item x="1230"/>
-        <item x="1231"/>
-        <item x="1232"/>
-        <item x="1233"/>
-        <item x="1234"/>
-        <item x="1235"/>
-        <item x="1236"/>
-        <item x="1237"/>
-        <item x="1238"/>
-        <item x="123"/>
-        <item x="1239"/>
-        <item x="1240"/>
-        <item x="1241"/>
-        <item x="1242"/>
-        <item x="1243"/>
-        <item x="1244"/>
-        <item x="1245"/>
-        <item x="1246"/>
-        <item x="1247"/>
-        <item x="1248"/>
-        <item x="124"/>
-        <item x="1249"/>
-        <item x="1250"/>
-        <item x="1251"/>
-        <item x="1252"/>
-        <item x="1253"/>
-        <item x="1254"/>
-        <item x="1255"/>
-        <item x="1256"/>
-        <item x="1257"/>
-        <item x="1258"/>
-        <item x="125"/>
-        <item x="1259"/>
-        <item x="1260"/>
-        <item x="1261"/>
-        <item x="1262"/>
-        <item x="1263"/>
-        <item x="1264"/>
-        <item x="1265"/>
-        <item x="1266"/>
-        <item x="1267"/>
-        <item x="1268"/>
-        <item x="126"/>
-        <item x="1269"/>
-        <item x="1270"/>
-        <item x="1271"/>
-        <item x="1272"/>
-        <item x="1273"/>
-        <item x="1274"/>
-        <item x="1275"/>
-        <item x="1276"/>
-        <item x="1277"/>
-        <item x="1278"/>
-        <item x="127"/>
-        <item x="1279"/>
-        <item x="1280"/>
-        <item x="1281"/>
-        <item x="1282"/>
-        <item x="1283"/>
-        <item x="1284"/>
-        <item x="1285"/>
-        <item x="1286"/>
-        <item x="1287"/>
-        <item x="1288"/>
-        <item x="128"/>
-        <item x="1289"/>
-        <item x="1290"/>
-        <item x="1291"/>
-        <item x="1292"/>
-        <item x="1293"/>
-        <item x="1294"/>
-        <item x="1295"/>
-        <item x="1296"/>
-        <item x="1297"/>
-        <item x="1298"/>
-        <item x="12"/>
-        <item x="129"/>
-        <item x="1299"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="13"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="14"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="15"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="16"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="17"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="18"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="1"/>
-        <item x="19"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="20"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="21"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="22"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="23"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="24"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="25"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="26"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="27"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="28"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="2"/>
-        <item x="29"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="30"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="31"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="32"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="33"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="34"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="35"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item x="368"/>
-        <item x="36"/>
-        <item x="369"/>
-        <item x="370"/>
-        <item x="371"/>
-        <item x="372"/>
-        <item x="373"/>
-        <item x="374"/>
-        <item x="375"/>
-        <item x="376"/>
-        <item x="377"/>
-        <item x="378"/>
-        <item x="37"/>
-        <item x="379"/>
-        <item x="380"/>
-        <item x="381"/>
-        <item x="382"/>
-        <item x="383"/>
-        <item x="384"/>
-        <item x="385"/>
-        <item x="386"/>
-        <item x="387"/>
-        <item x="388"/>
-        <item x="38"/>
-        <item x="389"/>
-        <item x="390"/>
-        <item x="391"/>
-        <item x="392"/>
-        <item x="393"/>
-        <item x="394"/>
-        <item x="395"/>
-        <item x="396"/>
-        <item x="397"/>
-        <item x="398"/>
-        <item x="3"/>
-        <item x="39"/>
-        <item x="399"/>
-        <item x="400"/>
-        <item x="401"/>
-        <item x="402"/>
-        <item x="403"/>
-        <item x="404"/>
-        <item x="405"/>
-        <item x="406"/>
-        <item x="407"/>
-        <item x="408"/>
-        <item x="40"/>
-        <item x="409"/>
-        <item x="410"/>
-        <item x="411"/>
-        <item x="412"/>
-        <item x="413"/>
-        <item x="414"/>
-        <item x="415"/>
-        <item x="416"/>
-        <item x="417"/>
-        <item x="418"/>
-        <item x="41"/>
-        <item x="419"/>
-        <item x="420"/>
-        <item x="421"/>
-        <item x="422"/>
-        <item x="423"/>
-        <item x="424"/>
-        <item x="425"/>
-        <item x="426"/>
-        <item x="427"/>
-        <item x="428"/>
-        <item x="42"/>
-        <item x="429"/>
-        <item x="430"/>
-        <item x="431"/>
-        <item x="432"/>
-        <item x="433"/>
-        <item x="434"/>
-        <item x="435"/>
-        <item x="436"/>
-        <item x="437"/>
-        <item x="438"/>
-        <item x="43"/>
-        <item x="439"/>
-        <item x="440"/>
-        <item x="441"/>
-        <item x="442"/>
-        <item x="443"/>
-        <item x="444"/>
-        <item x="445"/>
-        <item x="446"/>
-        <item x="447"/>
-        <item x="448"/>
-        <item x="44"/>
-        <item x="449"/>
-        <item x="450"/>
-        <item x="451"/>
-        <item x="452"/>
-        <item x="453"/>
-        <item x="454"/>
-        <item x="455"/>
-        <item x="456"/>
-        <item x="457"/>
-        <item x="458"/>
-        <item x="45"/>
-        <item x="459"/>
-        <item x="460"/>
-        <item x="461"/>
-        <item x="462"/>
-        <item x="463"/>
-        <item x="464"/>
-        <item x="465"/>
-        <item x="466"/>
-        <item x="467"/>
-        <item x="468"/>
-        <item x="46"/>
-        <item x="469"/>
-        <item x="470"/>
-        <item x="471"/>
-        <item x="472"/>
-        <item x="473"/>
-        <item x="474"/>
-        <item x="475"/>
-        <item x="476"/>
-        <item x="477"/>
-        <item x="478"/>
-        <item x="47"/>
-        <item x="479"/>
-        <item x="480"/>
-        <item x="481"/>
-        <item x="482"/>
-        <item x="483"/>
-        <item x="484"/>
-        <item x="485"/>
-        <item x="486"/>
-        <item x="487"/>
-        <item x="488"/>
-        <item x="48"/>
-        <item x="489"/>
-        <item x="490"/>
-        <item x="491"/>
-        <item x="492"/>
-        <item x="493"/>
-        <item x="494"/>
-        <item x="495"/>
-        <item x="496"/>
-        <item x="497"/>
-        <item x="498"/>
-        <item x="4"/>
-        <item x="49"/>
-        <item x="499"/>
-        <item x="500"/>
-        <item x="501"/>
-        <item x="502"/>
-        <item x="503"/>
-        <item x="504"/>
-        <item x="505"/>
-        <item x="506"/>
-        <item x="507"/>
-        <item x="508"/>
-        <item x="50"/>
-        <item x="509"/>
-        <item x="510"/>
-        <item x="511"/>
-        <item x="512"/>
-        <item x="513"/>
-        <item x="514"/>
-        <item x="515"/>
-        <item x="516"/>
-        <item x="517"/>
-        <item x="518"/>
-        <item x="51"/>
-        <item x="519"/>
-        <item x="520"/>
-        <item x="521"/>
-        <item x="522"/>
-        <item x="523"/>
-        <item x="524"/>
-        <item x="525"/>
-        <item x="526"/>
-        <item x="527"/>
-        <item x="528"/>
-        <item x="52"/>
-        <item x="529"/>
-        <item x="530"/>
-        <item x="531"/>
-        <item x="532"/>
-        <item x="533"/>
-        <item x="534"/>
-        <item x="535"/>
-        <item x="536"/>
-        <item x="537"/>
-        <item x="538"/>
-        <item x="53"/>
-        <item x="539"/>
-        <item x="540"/>
-        <item x="541"/>
-        <item x="542"/>
-        <item x="543"/>
-        <item x="544"/>
-        <item x="545"/>
-        <item x="546"/>
-        <item x="547"/>
-        <item x="548"/>
-        <item x="54"/>
-        <item x="549"/>
-        <item x="550"/>
-        <item x="551"/>
-        <item x="552"/>
-        <item x="553"/>
-        <item x="554"/>
-        <item x="555"/>
-        <item x="556"/>
-        <item x="557"/>
-        <item x="558"/>
-        <item x="55"/>
-        <item x="559"/>
-        <item x="560"/>
-        <item x="561"/>
-        <item x="562"/>
-        <item x="563"/>
-        <item x="564"/>
-        <item x="565"/>
-        <item x="566"/>
-        <item x="567"/>
-        <item x="568"/>
-        <item x="56"/>
-        <item x="569"/>
-        <item x="570"/>
-        <item x="571"/>
-        <item x="572"/>
-        <item x="573"/>
-        <item x="574"/>
-        <item x="575"/>
-        <item x="576"/>
-        <item x="577"/>
-        <item x="578"/>
-        <item x="57"/>
-        <item x="579"/>
-        <item x="580"/>
-        <item x="581"/>
-        <item x="582"/>
-        <item x="583"/>
-        <item x="584"/>
-        <item x="585"/>
-        <item x="586"/>
-        <item x="587"/>
-        <item x="588"/>
-        <item x="58"/>
-        <item x="589"/>
-        <item x="590"/>
-        <item x="591"/>
-        <item x="592"/>
-        <item x="593"/>
-        <item x="594"/>
-        <item x="595"/>
-        <item x="596"/>
-        <item x="597"/>
-        <item x="598"/>
-        <item x="5"/>
-        <item x="59"/>
-        <item x="599"/>
-        <item x="600"/>
-        <item x="601"/>
-        <item x="602"/>
-        <item x="603"/>
-        <item x="604"/>
-        <item x="605"/>
-        <item x="606"/>
-        <item x="607"/>
-        <item x="608"/>
-        <item x="60"/>
-        <item x="609"/>
-        <item x="610"/>
-        <item x="611"/>
-        <item x="612"/>
-        <item x="613"/>
-        <item x="614"/>
-        <item x="615"/>
-        <item x="616"/>
-        <item x="617"/>
-        <item x="618"/>
-        <item x="61"/>
-        <item x="619"/>
-        <item x="620"/>
-        <item x="621"/>
-        <item x="622"/>
-        <item x="623"/>
-        <item x="624"/>
-        <item x="625"/>
-        <item x="626"/>
-        <item x="627"/>
-        <item x="628"/>
-        <item x="62"/>
-        <item x="629"/>
-        <item x="630"/>
-        <item x="631"/>
-        <item x="632"/>
-        <item x="633"/>
-        <item x="634"/>
-        <item x="635"/>
-        <item x="636"/>
-        <item x="637"/>
-        <item x="638"/>
-        <item x="63"/>
-        <item x="639"/>
-        <item x="640"/>
-        <item x="641"/>
-        <item x="642"/>
-        <item x="643"/>
-        <item x="644"/>
-        <item x="645"/>
-        <item x="646"/>
-        <item x="647"/>
-        <item x="648"/>
-        <item x="64"/>
-        <item x="649"/>
-        <item x="650"/>
-        <item x="651"/>
-        <item x="652"/>
-        <item x="653"/>
-        <item x="654"/>
-        <item x="655"/>
-        <item x="656"/>
-        <item x="657"/>
-        <item x="658"/>
-        <item x="65"/>
-        <item x="659"/>
-        <item x="660"/>
-        <item x="661"/>
-        <item x="662"/>
-        <item x="663"/>
-        <item x="664"/>
-        <item x="665"/>
-        <item x="666"/>
-        <item x="667"/>
-        <item x="668"/>
-        <item x="66"/>
-        <item x="669"/>
-        <item x="670"/>
-        <item x="671"/>
-        <item x="672"/>
-        <item x="673"/>
-        <item x="674"/>
-        <item x="675"/>
-        <item x="676"/>
-        <item x="677"/>
-        <item x="678"/>
-        <item x="67"/>
-        <item x="679"/>
-        <item x="680"/>
-        <item x="681"/>
-        <item x="682"/>
-        <item x="683"/>
-        <item x="684"/>
-        <item x="685"/>
-        <item x="686"/>
-        <item x="687"/>
-        <item x="688"/>
-        <item x="68"/>
-        <item x="689"/>
-        <item x="690"/>
-        <item x="691"/>
-        <item x="692"/>
-        <item x="693"/>
-        <item x="694"/>
-        <item x="695"/>
-        <item x="696"/>
-        <item x="697"/>
-        <item x="698"/>
-        <item x="6"/>
-        <item x="69"/>
-        <item x="699"/>
-        <item x="700"/>
-        <item x="701"/>
-        <item x="702"/>
-        <item x="703"/>
-        <item x="704"/>
-        <item x="705"/>
-        <item x="706"/>
-        <item x="707"/>
-        <item x="708"/>
-        <item x="70"/>
-        <item x="709"/>
-        <item x="710"/>
-        <item x="711"/>
-        <item x="712"/>
-        <item x="713"/>
-        <item x="714"/>
-        <item x="715"/>
-        <item x="716"/>
-        <item x="717"/>
-        <item x="718"/>
-        <item x="71"/>
-        <item x="719"/>
-        <item x="720"/>
-        <item x="721"/>
-        <item x="722"/>
-        <item x="723"/>
-        <item x="724"/>
-        <item x="725"/>
-        <item x="726"/>
-        <item x="727"/>
-        <item x="728"/>
-        <item x="72"/>
-        <item x="729"/>
-        <item x="730"/>
-        <item x="731"/>
-        <item x="732"/>
-        <item x="733"/>
-        <item x="734"/>
-        <item x="735"/>
-        <item x="736"/>
-        <item x="737"/>
-        <item x="738"/>
-        <item x="73"/>
-        <item x="739"/>
-        <item x="740"/>
-        <item x="741"/>
-        <item x="742"/>
-        <item x="743"/>
-        <item x="744"/>
-        <item x="745"/>
-        <item x="746"/>
-        <item x="747"/>
-        <item x="748"/>
-        <item x="74"/>
-        <item x="749"/>
-        <item x="750"/>
-        <item x="751"/>
-        <item x="752"/>
-        <item x="753"/>
-        <item x="754"/>
-        <item x="755"/>
-        <item x="756"/>
-        <item x="757"/>
-        <item x="758"/>
-        <item x="75"/>
-        <item x="759"/>
-        <item x="760"/>
-        <item x="761"/>
-        <item x="762"/>
-        <item x="763"/>
-        <item x="764"/>
-        <item x="765"/>
-        <item x="766"/>
-        <item x="767"/>
-        <item x="768"/>
-        <item x="76"/>
-        <item x="769"/>
-        <item x="770"/>
-        <item x="771"/>
-        <item x="772"/>
-        <item x="773"/>
-        <item x="774"/>
-        <item x="775"/>
-        <item x="776"/>
-        <item x="777"/>
-        <item x="778"/>
-        <item x="77"/>
-        <item x="779"/>
-        <item x="780"/>
-        <item x="781"/>
-        <item x="782"/>
-        <item x="783"/>
-        <item x="784"/>
-        <item x="785"/>
-        <item x="786"/>
-        <item x="787"/>
-        <item x="788"/>
-        <item x="78"/>
-        <item x="789"/>
-        <item x="790"/>
-        <item x="791"/>
-        <item x="792"/>
-        <item x="793"/>
-        <item x="794"/>
-        <item x="795"/>
-        <item x="796"/>
-        <item x="797"/>
-        <item x="798"/>
-        <item x="7"/>
-        <item x="79"/>
-        <item x="799"/>
-        <item x="800"/>
-        <item x="801"/>
-        <item x="802"/>
-        <item x="803"/>
-        <item x="804"/>
-        <item x="805"/>
-        <item x="806"/>
-        <item x="807"/>
-        <item x="808"/>
-        <item x="80"/>
-        <item x="809"/>
-        <item x="810"/>
-        <item x="811"/>
-        <item x="812"/>
-        <item x="813"/>
-        <item x="814"/>
-        <item x="815"/>
-        <item x="816"/>
-        <item x="817"/>
-        <item x="818"/>
-        <item x="81"/>
-        <item x="819"/>
-        <item x="820"/>
-        <item x="821"/>
-        <item x="822"/>
-        <item x="823"/>
-        <item x="824"/>
-        <item x="825"/>
-        <item x="826"/>
-        <item x="827"/>
-        <item x="828"/>
-        <item x="82"/>
-        <item x="829"/>
-        <item x="830"/>
-        <item x="831"/>
-        <item x="832"/>
-        <item x="833"/>
-        <item x="834"/>
-        <item x="835"/>
-        <item x="836"/>
-        <item x="837"/>
-        <item x="838"/>
-        <item x="83"/>
-        <item x="839"/>
-        <item x="840"/>
-        <item x="841"/>
-        <item x="842"/>
-        <item x="843"/>
-        <item x="844"/>
-        <item x="845"/>
-        <item x="846"/>
-        <item x="847"/>
-        <item x="848"/>
-        <item x="84"/>
-        <item x="849"/>
-        <item x="850"/>
-        <item x="851"/>
-        <item x="852"/>
-        <item x="853"/>
-        <item x="854"/>
-        <item x="855"/>
-        <item x="856"/>
-        <item x="857"/>
-        <item x="858"/>
-        <item x="85"/>
-        <item x="859"/>
-        <item x="860"/>
-        <item x="861"/>
-        <item x="862"/>
-        <item x="863"/>
-        <item x="864"/>
-        <item x="865"/>
-        <item x="866"/>
-        <item x="867"/>
-        <item x="868"/>
-        <item x="86"/>
-        <item x="869"/>
-        <item x="870"/>
-        <item x="871"/>
-        <item x="872"/>
-        <item x="873"/>
-        <item x="874"/>
-        <item x="875"/>
-        <item x="876"/>
-        <item x="877"/>
-        <item x="878"/>
-        <item x="87"/>
-        <item x="879"/>
-        <item x="880"/>
-        <item x="881"/>
-        <item x="882"/>
-        <item x="883"/>
-        <item x="884"/>
-        <item x="885"/>
-        <item x="886"/>
-        <item x="887"/>
-        <item x="888"/>
-        <item x="88"/>
-        <item x="889"/>
-        <item x="890"/>
-        <item x="891"/>
-        <item x="892"/>
-        <item x="893"/>
-        <item x="894"/>
-        <item x="895"/>
-        <item x="896"/>
-        <item x="897"/>
-        <item x="898"/>
-        <item x="8"/>
-        <item x="89"/>
-        <item x="899"/>
-        <item x="900"/>
-        <item x="901"/>
-        <item x="902"/>
-        <item x="903"/>
-        <item x="904"/>
-        <item x="905"/>
-        <item x="906"/>
-        <item x="907"/>
-        <item x="908"/>
-        <item x="90"/>
-        <item x="909"/>
-        <item x="910"/>
-        <item x="911"/>
-        <item x="912"/>
-        <item x="913"/>
-        <item x="914"/>
-        <item x="915"/>
-        <item x="916"/>
-        <item x="917"/>
-        <item x="918"/>
-        <item x="91"/>
-        <item x="919"/>
-        <item x="920"/>
-        <item x="921"/>
-        <item x="922"/>
-        <item x="923"/>
-        <item x="924"/>
-        <item x="925"/>
-        <item x="926"/>
-        <item x="927"/>
-        <item x="928"/>
-        <item x="92"/>
-        <item x="929"/>
-        <item x="930"/>
-        <item x="931"/>
-        <item x="932"/>
-        <item x="933"/>
-        <item x="934"/>
-        <item x="935"/>
-        <item x="936"/>
-        <item x="937"/>
-        <item x="938"/>
-        <item x="93"/>
-        <item x="939"/>
-        <item x="940"/>
-        <item x="941"/>
-        <item x="942"/>
-        <item x="943"/>
-        <item x="944"/>
-        <item x="945"/>
-        <item x="946"/>
-        <item x="947"/>
-        <item x="948"/>
-        <item x="94"/>
-        <item x="949"/>
-        <item x="950"/>
-        <item x="951"/>
-        <item x="952"/>
-        <item x="953"/>
-        <item x="954"/>
-        <item x="955"/>
-        <item x="956"/>
-        <item x="957"/>
-        <item x="958"/>
-        <item x="95"/>
-        <item x="959"/>
-        <item x="960"/>
-        <item x="961"/>
-        <item x="962"/>
-        <item x="963"/>
-        <item x="964"/>
-        <item x="965"/>
-        <item x="966"/>
-        <item x="967"/>
-        <item x="968"/>
-        <item x="96"/>
-        <item x="969"/>
-        <item x="970"/>
-        <item x="971"/>
-        <item x="972"/>
-        <item x="973"/>
-        <item x="974"/>
-        <item x="975"/>
-        <item x="976"/>
-        <item x="977"/>
-        <item x="978"/>
-        <item x="97"/>
-        <item x="979"/>
-        <item x="980"/>
-        <item x="981"/>
-        <item x="982"/>
-        <item x="983"/>
-        <item x="984"/>
-        <item x="985"/>
-        <item x="986"/>
-        <item x="987"/>
-        <item x="988"/>
-        <item x="98"/>
-        <item x="989"/>
-        <item x="990"/>
-        <item x="991"/>
-        <item x="992"/>
-        <item x="993"/>
-        <item x="994"/>
-        <item x="995"/>
-        <item x="996"/>
-        <item x="997"/>
-        <item x="998"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total commissions" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="6">
-    <format dxfId="75">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="74">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="73">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="72">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="71">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="70">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13801BD3-C489-4167-BC3B-FAD8CE7DB4D7}" name="PivotTable7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13801BD3-C489-4167-BC3B-FAD8CE7DB4D7}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="19">
   <location ref="A54:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -39651,22 +35192,22 @@
     <dataField name="Sum of Quantity" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="81">
+    <format dxfId="5">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="2">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="77">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -39702,8 +35243,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{693A281E-64CF-4729-98FD-B8F371C0E96E}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{693A281E-64CF-4729-98FD-B8F371C0E96E}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A4" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
     <pivotField dataField="1" showAll="0">
@@ -41031,31 +36572,31 @@
     <dataField name="Total Order" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="90">
+    <format dxfId="14">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="89">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="8">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="83">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="82">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -41071,8 +36612,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCB6DE82-853E-48F7-982D-5172FFB139C4}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BCB6DE82-853E-48F7-982D-5172FFB139C4}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="A19:B51" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -42786,22 +38327,22 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="96">
+    <format dxfId="20">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="95">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="93">
+    <format dxfId="17">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -42837,8 +38378,2960 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0324B6A6-8E31-4843-B69E-3CBA9D29CB07}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3C16518-6C6B-401F-9B59-4FD81C70871C}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22">
+  <location ref="A100:B113" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField dataField="1" showAll="0">
+      <items count="1301">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="99"/>
+        <item x="999"/>
+        <item x="1000"/>
+        <item x="1001"/>
+        <item x="1002"/>
+        <item x="1003"/>
+        <item x="1004"/>
+        <item x="1005"/>
+        <item x="1006"/>
+        <item x="1007"/>
+        <item x="1008"/>
+        <item x="100"/>
+        <item x="1009"/>
+        <item x="1010"/>
+        <item x="1011"/>
+        <item x="1012"/>
+        <item x="1013"/>
+        <item x="1014"/>
+        <item x="1015"/>
+        <item x="1016"/>
+        <item x="1017"/>
+        <item x="1018"/>
+        <item x="101"/>
+        <item x="1019"/>
+        <item x="1020"/>
+        <item x="1021"/>
+        <item x="1022"/>
+        <item x="1023"/>
+        <item x="1024"/>
+        <item x="1025"/>
+        <item x="1026"/>
+        <item x="1027"/>
+        <item x="1028"/>
+        <item x="102"/>
+        <item x="1029"/>
+        <item x="1030"/>
+        <item x="1031"/>
+        <item x="1032"/>
+        <item x="1033"/>
+        <item x="1034"/>
+        <item x="1035"/>
+        <item x="1036"/>
+        <item x="1037"/>
+        <item x="1038"/>
+        <item x="103"/>
+        <item x="1039"/>
+        <item x="1040"/>
+        <item x="1041"/>
+        <item x="1042"/>
+        <item x="1043"/>
+        <item x="1044"/>
+        <item x="1045"/>
+        <item x="1046"/>
+        <item x="1047"/>
+        <item x="1048"/>
+        <item x="104"/>
+        <item x="1049"/>
+        <item x="1050"/>
+        <item x="1051"/>
+        <item x="1052"/>
+        <item x="1053"/>
+        <item x="1054"/>
+        <item x="1055"/>
+        <item x="1056"/>
+        <item x="1057"/>
+        <item x="1058"/>
+        <item x="105"/>
+        <item x="1059"/>
+        <item x="1060"/>
+        <item x="1061"/>
+        <item x="1062"/>
+        <item x="1063"/>
+        <item x="1064"/>
+        <item x="1065"/>
+        <item x="1066"/>
+        <item x="1067"/>
+        <item x="1068"/>
+        <item x="106"/>
+        <item x="1069"/>
+        <item x="1070"/>
+        <item x="1071"/>
+        <item x="1072"/>
+        <item x="1073"/>
+        <item x="1074"/>
+        <item x="1075"/>
+        <item x="1076"/>
+        <item x="1077"/>
+        <item x="1078"/>
+        <item x="107"/>
+        <item x="1079"/>
+        <item x="1080"/>
+        <item x="1081"/>
+        <item x="1082"/>
+        <item x="1083"/>
+        <item x="1084"/>
+        <item x="1085"/>
+        <item x="1086"/>
+        <item x="1087"/>
+        <item x="1088"/>
+        <item x="108"/>
+        <item x="1089"/>
+        <item x="1090"/>
+        <item x="1091"/>
+        <item x="1092"/>
+        <item x="1093"/>
+        <item x="1094"/>
+        <item x="1095"/>
+        <item x="1096"/>
+        <item x="1097"/>
+        <item x="1098"/>
+        <item x="10"/>
+        <item x="109"/>
+        <item x="1099"/>
+        <item x="1100"/>
+        <item x="1101"/>
+        <item x="1102"/>
+        <item x="1103"/>
+        <item x="1104"/>
+        <item x="1105"/>
+        <item x="1106"/>
+        <item x="1107"/>
+        <item x="1108"/>
+        <item x="110"/>
+        <item x="1109"/>
+        <item x="1110"/>
+        <item x="1111"/>
+        <item x="1112"/>
+        <item x="1113"/>
+        <item x="1114"/>
+        <item x="1115"/>
+        <item x="1116"/>
+        <item x="1117"/>
+        <item x="1118"/>
+        <item x="111"/>
+        <item x="1119"/>
+        <item x="1120"/>
+        <item x="1121"/>
+        <item x="1122"/>
+        <item x="1123"/>
+        <item x="1124"/>
+        <item x="1125"/>
+        <item x="1126"/>
+        <item x="1127"/>
+        <item x="1128"/>
+        <item x="112"/>
+        <item x="1129"/>
+        <item x="1130"/>
+        <item x="1131"/>
+        <item x="1132"/>
+        <item x="1133"/>
+        <item x="1134"/>
+        <item x="1135"/>
+        <item x="1136"/>
+        <item x="1137"/>
+        <item x="1138"/>
+        <item x="113"/>
+        <item x="1139"/>
+        <item x="1140"/>
+        <item x="1141"/>
+        <item x="1142"/>
+        <item x="1143"/>
+        <item x="1144"/>
+        <item x="1145"/>
+        <item x="1146"/>
+        <item x="1147"/>
+        <item x="1148"/>
+        <item x="114"/>
+        <item x="1149"/>
+        <item x="1150"/>
+        <item x="1151"/>
+        <item x="1152"/>
+        <item x="1153"/>
+        <item x="1154"/>
+        <item x="1155"/>
+        <item x="1156"/>
+        <item x="1157"/>
+        <item x="1158"/>
+        <item x="115"/>
+        <item x="1159"/>
+        <item x="1160"/>
+        <item x="1161"/>
+        <item x="1162"/>
+        <item x="1163"/>
+        <item x="1164"/>
+        <item x="1165"/>
+        <item x="1166"/>
+        <item x="1167"/>
+        <item x="1168"/>
+        <item x="116"/>
+        <item x="1169"/>
+        <item x="1170"/>
+        <item x="1171"/>
+        <item x="1172"/>
+        <item x="1173"/>
+        <item x="1174"/>
+        <item x="1175"/>
+        <item x="1176"/>
+        <item x="1177"/>
+        <item x="1178"/>
+        <item x="117"/>
+        <item x="1179"/>
+        <item x="1180"/>
+        <item x="1181"/>
+        <item x="1182"/>
+        <item x="1183"/>
+        <item x="1184"/>
+        <item x="1185"/>
+        <item x="1186"/>
+        <item x="1187"/>
+        <item x="1188"/>
+        <item x="118"/>
+        <item x="1189"/>
+        <item x="1190"/>
+        <item x="1191"/>
+        <item x="1192"/>
+        <item x="1193"/>
+        <item x="1194"/>
+        <item x="1195"/>
+        <item x="1196"/>
+        <item x="1197"/>
+        <item x="1198"/>
+        <item x="11"/>
+        <item x="119"/>
+        <item x="1199"/>
+        <item x="1200"/>
+        <item x="1201"/>
+        <item x="1202"/>
+        <item x="1203"/>
+        <item x="1204"/>
+        <item x="1205"/>
+        <item x="1206"/>
+        <item x="1207"/>
+        <item x="1208"/>
+        <item x="120"/>
+        <item x="1209"/>
+        <item x="1210"/>
+        <item x="1211"/>
+        <item x="1212"/>
+        <item x="1213"/>
+        <item x="1214"/>
+        <item x="1215"/>
+        <item x="1216"/>
+        <item x="1217"/>
+        <item x="1218"/>
+        <item x="121"/>
+        <item x="1219"/>
+        <item x="1220"/>
+        <item x="1221"/>
+        <item x="1222"/>
+        <item x="1223"/>
+        <item x="1224"/>
+        <item x="1225"/>
+        <item x="1226"/>
+        <item x="1227"/>
+        <item x="1228"/>
+        <item x="122"/>
+        <item x="1229"/>
+        <item x="1230"/>
+        <item x="1231"/>
+        <item x="1232"/>
+        <item x="1233"/>
+        <item x="1234"/>
+        <item x="1235"/>
+        <item x="1236"/>
+        <item x="1237"/>
+        <item x="1238"/>
+        <item x="123"/>
+        <item x="1239"/>
+        <item x="1240"/>
+        <item x="1241"/>
+        <item x="1242"/>
+        <item x="1243"/>
+        <item x="1244"/>
+        <item x="1245"/>
+        <item x="1246"/>
+        <item x="1247"/>
+        <item x="1248"/>
+        <item x="124"/>
+        <item x="1249"/>
+        <item x="1250"/>
+        <item x="1251"/>
+        <item x="1252"/>
+        <item x="1253"/>
+        <item x="1254"/>
+        <item x="1255"/>
+        <item x="1256"/>
+        <item x="1257"/>
+        <item x="1258"/>
+        <item x="125"/>
+        <item x="1259"/>
+        <item x="1260"/>
+        <item x="1261"/>
+        <item x="1262"/>
+        <item x="1263"/>
+        <item x="1264"/>
+        <item x="1265"/>
+        <item x="1266"/>
+        <item x="1267"/>
+        <item x="1268"/>
+        <item x="126"/>
+        <item x="1269"/>
+        <item x="1270"/>
+        <item x="1271"/>
+        <item x="1272"/>
+        <item x="1273"/>
+        <item x="1274"/>
+        <item x="1275"/>
+        <item x="1276"/>
+        <item x="1277"/>
+        <item x="1278"/>
+        <item x="127"/>
+        <item x="1279"/>
+        <item x="1280"/>
+        <item x="1281"/>
+        <item x="1282"/>
+        <item x="1283"/>
+        <item x="1284"/>
+        <item x="1285"/>
+        <item x="1286"/>
+        <item x="1287"/>
+        <item x="1288"/>
+        <item x="128"/>
+        <item x="1289"/>
+        <item x="1290"/>
+        <item x="1291"/>
+        <item x="1292"/>
+        <item x="1293"/>
+        <item x="1294"/>
+        <item x="1295"/>
+        <item x="1296"/>
+        <item x="1297"/>
+        <item x="1298"/>
+        <item x="12"/>
+        <item x="129"/>
+        <item x="1299"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="13"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="14"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="15"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="16"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="17"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="18"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="20"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="21"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="22"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="23"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="24"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="25"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="26"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="27"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="28"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="30"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="31"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="32"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="33"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="34"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="35"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="36"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="37"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="38"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="3"/>
+        <item x="39"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="40"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="41"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="42"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="43"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="44"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="45"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="46"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="47"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="48"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item x="4"/>
+        <item x="49"/>
+        <item x="499"/>
+        <item x="500"/>
+        <item x="501"/>
+        <item x="502"/>
+        <item x="503"/>
+        <item x="504"/>
+        <item x="505"/>
+        <item x="506"/>
+        <item x="507"/>
+        <item x="508"/>
+        <item x="50"/>
+        <item x="509"/>
+        <item x="510"/>
+        <item x="511"/>
+        <item x="512"/>
+        <item x="513"/>
+        <item x="514"/>
+        <item x="515"/>
+        <item x="516"/>
+        <item x="517"/>
+        <item x="518"/>
+        <item x="51"/>
+        <item x="519"/>
+        <item x="520"/>
+        <item x="521"/>
+        <item x="522"/>
+        <item x="523"/>
+        <item x="524"/>
+        <item x="525"/>
+        <item x="526"/>
+        <item x="527"/>
+        <item x="528"/>
+        <item x="52"/>
+        <item x="529"/>
+        <item x="530"/>
+        <item x="531"/>
+        <item x="532"/>
+        <item x="533"/>
+        <item x="534"/>
+        <item x="535"/>
+        <item x="536"/>
+        <item x="537"/>
+        <item x="538"/>
+        <item x="53"/>
+        <item x="539"/>
+        <item x="540"/>
+        <item x="541"/>
+        <item x="542"/>
+        <item x="543"/>
+        <item x="544"/>
+        <item x="545"/>
+        <item x="546"/>
+        <item x="547"/>
+        <item x="548"/>
+        <item x="54"/>
+        <item x="549"/>
+        <item x="550"/>
+        <item x="551"/>
+        <item x="552"/>
+        <item x="553"/>
+        <item x="554"/>
+        <item x="555"/>
+        <item x="556"/>
+        <item x="557"/>
+        <item x="558"/>
+        <item x="55"/>
+        <item x="559"/>
+        <item x="560"/>
+        <item x="561"/>
+        <item x="562"/>
+        <item x="563"/>
+        <item x="564"/>
+        <item x="565"/>
+        <item x="566"/>
+        <item x="567"/>
+        <item x="568"/>
+        <item x="56"/>
+        <item x="569"/>
+        <item x="570"/>
+        <item x="571"/>
+        <item x="572"/>
+        <item x="573"/>
+        <item x="574"/>
+        <item x="575"/>
+        <item x="576"/>
+        <item x="577"/>
+        <item x="578"/>
+        <item x="57"/>
+        <item x="579"/>
+        <item x="580"/>
+        <item x="581"/>
+        <item x="582"/>
+        <item x="583"/>
+        <item x="584"/>
+        <item x="585"/>
+        <item x="586"/>
+        <item x="587"/>
+        <item x="588"/>
+        <item x="58"/>
+        <item x="589"/>
+        <item x="590"/>
+        <item x="591"/>
+        <item x="592"/>
+        <item x="593"/>
+        <item x="594"/>
+        <item x="595"/>
+        <item x="596"/>
+        <item x="597"/>
+        <item x="598"/>
+        <item x="5"/>
+        <item x="59"/>
+        <item x="599"/>
+        <item x="600"/>
+        <item x="601"/>
+        <item x="602"/>
+        <item x="603"/>
+        <item x="604"/>
+        <item x="605"/>
+        <item x="606"/>
+        <item x="607"/>
+        <item x="608"/>
+        <item x="60"/>
+        <item x="609"/>
+        <item x="610"/>
+        <item x="611"/>
+        <item x="612"/>
+        <item x="613"/>
+        <item x="614"/>
+        <item x="615"/>
+        <item x="616"/>
+        <item x="617"/>
+        <item x="618"/>
+        <item x="61"/>
+        <item x="619"/>
+        <item x="620"/>
+        <item x="621"/>
+        <item x="622"/>
+        <item x="623"/>
+        <item x="624"/>
+        <item x="625"/>
+        <item x="626"/>
+        <item x="627"/>
+        <item x="628"/>
+        <item x="62"/>
+        <item x="629"/>
+        <item x="630"/>
+        <item x="631"/>
+        <item x="632"/>
+        <item x="633"/>
+        <item x="634"/>
+        <item x="635"/>
+        <item x="636"/>
+        <item x="637"/>
+        <item x="638"/>
+        <item x="63"/>
+        <item x="639"/>
+        <item x="640"/>
+        <item x="641"/>
+        <item x="642"/>
+        <item x="643"/>
+        <item x="644"/>
+        <item x="645"/>
+        <item x="646"/>
+        <item x="647"/>
+        <item x="648"/>
+        <item x="64"/>
+        <item x="649"/>
+        <item x="650"/>
+        <item x="651"/>
+        <item x="652"/>
+        <item x="653"/>
+        <item x="654"/>
+        <item x="655"/>
+        <item x="656"/>
+        <item x="657"/>
+        <item x="658"/>
+        <item x="65"/>
+        <item x="659"/>
+        <item x="660"/>
+        <item x="661"/>
+        <item x="662"/>
+        <item x="663"/>
+        <item x="664"/>
+        <item x="665"/>
+        <item x="666"/>
+        <item x="667"/>
+        <item x="668"/>
+        <item x="66"/>
+        <item x="669"/>
+        <item x="670"/>
+        <item x="671"/>
+        <item x="672"/>
+        <item x="673"/>
+        <item x="674"/>
+        <item x="675"/>
+        <item x="676"/>
+        <item x="677"/>
+        <item x="678"/>
+        <item x="67"/>
+        <item x="679"/>
+        <item x="680"/>
+        <item x="681"/>
+        <item x="682"/>
+        <item x="683"/>
+        <item x="684"/>
+        <item x="685"/>
+        <item x="686"/>
+        <item x="687"/>
+        <item x="688"/>
+        <item x="68"/>
+        <item x="689"/>
+        <item x="690"/>
+        <item x="691"/>
+        <item x="692"/>
+        <item x="693"/>
+        <item x="694"/>
+        <item x="695"/>
+        <item x="696"/>
+        <item x="697"/>
+        <item x="698"/>
+        <item x="6"/>
+        <item x="69"/>
+        <item x="699"/>
+        <item x="700"/>
+        <item x="701"/>
+        <item x="702"/>
+        <item x="703"/>
+        <item x="704"/>
+        <item x="705"/>
+        <item x="706"/>
+        <item x="707"/>
+        <item x="708"/>
+        <item x="70"/>
+        <item x="709"/>
+        <item x="710"/>
+        <item x="711"/>
+        <item x="712"/>
+        <item x="713"/>
+        <item x="714"/>
+        <item x="715"/>
+        <item x="716"/>
+        <item x="717"/>
+        <item x="718"/>
+        <item x="71"/>
+        <item x="719"/>
+        <item x="720"/>
+        <item x="721"/>
+        <item x="722"/>
+        <item x="723"/>
+        <item x="724"/>
+        <item x="725"/>
+        <item x="726"/>
+        <item x="727"/>
+        <item x="728"/>
+        <item x="72"/>
+        <item x="729"/>
+        <item x="730"/>
+        <item x="731"/>
+        <item x="732"/>
+        <item x="733"/>
+        <item x="734"/>
+        <item x="735"/>
+        <item x="736"/>
+        <item x="737"/>
+        <item x="738"/>
+        <item x="73"/>
+        <item x="739"/>
+        <item x="740"/>
+        <item x="741"/>
+        <item x="742"/>
+        <item x="743"/>
+        <item x="744"/>
+        <item x="745"/>
+        <item x="746"/>
+        <item x="747"/>
+        <item x="748"/>
+        <item x="74"/>
+        <item x="749"/>
+        <item x="750"/>
+        <item x="751"/>
+        <item x="752"/>
+        <item x="753"/>
+        <item x="754"/>
+        <item x="755"/>
+        <item x="756"/>
+        <item x="757"/>
+        <item x="758"/>
+        <item x="75"/>
+        <item x="759"/>
+        <item x="760"/>
+        <item x="761"/>
+        <item x="762"/>
+        <item x="763"/>
+        <item x="764"/>
+        <item x="765"/>
+        <item x="766"/>
+        <item x="767"/>
+        <item x="768"/>
+        <item x="76"/>
+        <item x="769"/>
+        <item x="770"/>
+        <item x="771"/>
+        <item x="772"/>
+        <item x="773"/>
+        <item x="774"/>
+        <item x="775"/>
+        <item x="776"/>
+        <item x="777"/>
+        <item x="778"/>
+        <item x="77"/>
+        <item x="779"/>
+        <item x="780"/>
+        <item x="781"/>
+        <item x="782"/>
+        <item x="783"/>
+        <item x="784"/>
+        <item x="785"/>
+        <item x="786"/>
+        <item x="787"/>
+        <item x="788"/>
+        <item x="78"/>
+        <item x="789"/>
+        <item x="790"/>
+        <item x="791"/>
+        <item x="792"/>
+        <item x="793"/>
+        <item x="794"/>
+        <item x="795"/>
+        <item x="796"/>
+        <item x="797"/>
+        <item x="798"/>
+        <item x="7"/>
+        <item x="79"/>
+        <item x="799"/>
+        <item x="800"/>
+        <item x="801"/>
+        <item x="802"/>
+        <item x="803"/>
+        <item x="804"/>
+        <item x="805"/>
+        <item x="806"/>
+        <item x="807"/>
+        <item x="808"/>
+        <item x="80"/>
+        <item x="809"/>
+        <item x="810"/>
+        <item x="811"/>
+        <item x="812"/>
+        <item x="813"/>
+        <item x="814"/>
+        <item x="815"/>
+        <item x="816"/>
+        <item x="817"/>
+        <item x="818"/>
+        <item x="81"/>
+        <item x="819"/>
+        <item x="820"/>
+        <item x="821"/>
+        <item x="822"/>
+        <item x="823"/>
+        <item x="824"/>
+        <item x="825"/>
+        <item x="826"/>
+        <item x="827"/>
+        <item x="828"/>
+        <item x="82"/>
+        <item x="829"/>
+        <item x="830"/>
+        <item x="831"/>
+        <item x="832"/>
+        <item x="833"/>
+        <item x="834"/>
+        <item x="835"/>
+        <item x="836"/>
+        <item x="837"/>
+        <item x="838"/>
+        <item x="83"/>
+        <item x="839"/>
+        <item x="840"/>
+        <item x="841"/>
+        <item x="842"/>
+        <item x="843"/>
+        <item x="844"/>
+        <item x="845"/>
+        <item x="846"/>
+        <item x="847"/>
+        <item x="848"/>
+        <item x="84"/>
+        <item x="849"/>
+        <item x="850"/>
+        <item x="851"/>
+        <item x="852"/>
+        <item x="853"/>
+        <item x="854"/>
+        <item x="855"/>
+        <item x="856"/>
+        <item x="857"/>
+        <item x="858"/>
+        <item x="85"/>
+        <item x="859"/>
+        <item x="860"/>
+        <item x="861"/>
+        <item x="862"/>
+        <item x="863"/>
+        <item x="864"/>
+        <item x="865"/>
+        <item x="866"/>
+        <item x="867"/>
+        <item x="868"/>
+        <item x="86"/>
+        <item x="869"/>
+        <item x="870"/>
+        <item x="871"/>
+        <item x="872"/>
+        <item x="873"/>
+        <item x="874"/>
+        <item x="875"/>
+        <item x="876"/>
+        <item x="877"/>
+        <item x="878"/>
+        <item x="87"/>
+        <item x="879"/>
+        <item x="880"/>
+        <item x="881"/>
+        <item x="882"/>
+        <item x="883"/>
+        <item x="884"/>
+        <item x="885"/>
+        <item x="886"/>
+        <item x="887"/>
+        <item x="888"/>
+        <item x="88"/>
+        <item x="889"/>
+        <item x="890"/>
+        <item x="891"/>
+        <item x="892"/>
+        <item x="893"/>
+        <item x="894"/>
+        <item x="895"/>
+        <item x="896"/>
+        <item x="897"/>
+        <item x="898"/>
+        <item x="8"/>
+        <item x="89"/>
+        <item x="899"/>
+        <item x="900"/>
+        <item x="901"/>
+        <item x="902"/>
+        <item x="903"/>
+        <item x="904"/>
+        <item x="905"/>
+        <item x="906"/>
+        <item x="907"/>
+        <item x="908"/>
+        <item x="90"/>
+        <item x="909"/>
+        <item x="910"/>
+        <item x="911"/>
+        <item x="912"/>
+        <item x="913"/>
+        <item x="914"/>
+        <item x="915"/>
+        <item x="916"/>
+        <item x="917"/>
+        <item x="918"/>
+        <item x="91"/>
+        <item x="919"/>
+        <item x="920"/>
+        <item x="921"/>
+        <item x="922"/>
+        <item x="923"/>
+        <item x="924"/>
+        <item x="925"/>
+        <item x="926"/>
+        <item x="927"/>
+        <item x="928"/>
+        <item x="92"/>
+        <item x="929"/>
+        <item x="930"/>
+        <item x="931"/>
+        <item x="932"/>
+        <item x="933"/>
+        <item x="934"/>
+        <item x="935"/>
+        <item x="936"/>
+        <item x="937"/>
+        <item x="938"/>
+        <item x="93"/>
+        <item x="939"/>
+        <item x="940"/>
+        <item x="941"/>
+        <item x="942"/>
+        <item x="943"/>
+        <item x="944"/>
+        <item x="945"/>
+        <item x="946"/>
+        <item x="947"/>
+        <item x="948"/>
+        <item x="94"/>
+        <item x="949"/>
+        <item x="950"/>
+        <item x="951"/>
+        <item x="952"/>
+        <item x="953"/>
+        <item x="954"/>
+        <item x="955"/>
+        <item x="956"/>
+        <item x="957"/>
+        <item x="958"/>
+        <item x="95"/>
+        <item x="959"/>
+        <item x="960"/>
+        <item x="961"/>
+        <item x="962"/>
+        <item x="963"/>
+        <item x="964"/>
+        <item x="965"/>
+        <item x="966"/>
+        <item x="967"/>
+        <item x="968"/>
+        <item x="96"/>
+        <item x="969"/>
+        <item x="970"/>
+        <item x="971"/>
+        <item x="972"/>
+        <item x="973"/>
+        <item x="974"/>
+        <item x="975"/>
+        <item x="976"/>
+        <item x="977"/>
+        <item x="978"/>
+        <item x="97"/>
+        <item x="979"/>
+        <item x="980"/>
+        <item x="981"/>
+        <item x="982"/>
+        <item x="983"/>
+        <item x="984"/>
+        <item x="985"/>
+        <item x="986"/>
+        <item x="987"/>
+        <item x="988"/>
+        <item x="98"/>
+        <item x="989"/>
+        <item x="990"/>
+        <item x="991"/>
+        <item x="992"/>
+        <item x="993"/>
+        <item x="994"/>
+        <item x="995"/>
+        <item x="996"/>
+        <item x="997"/>
+        <item x="998"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="32">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="8"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order_Id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="21" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{030ED229-A10E-49DC-B1D7-4E2AE8584D8E}" name="PivotTable9" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="A82:B88" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField showAll="0">
+      <items count="1301">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="99"/>
+        <item x="999"/>
+        <item x="1000"/>
+        <item x="1001"/>
+        <item x="1002"/>
+        <item x="1003"/>
+        <item x="1004"/>
+        <item x="1005"/>
+        <item x="1006"/>
+        <item x="1007"/>
+        <item x="1008"/>
+        <item x="100"/>
+        <item x="1009"/>
+        <item x="1010"/>
+        <item x="1011"/>
+        <item x="1012"/>
+        <item x="1013"/>
+        <item x="1014"/>
+        <item x="1015"/>
+        <item x="1016"/>
+        <item x="1017"/>
+        <item x="1018"/>
+        <item x="101"/>
+        <item x="1019"/>
+        <item x="1020"/>
+        <item x="1021"/>
+        <item x="1022"/>
+        <item x="1023"/>
+        <item x="1024"/>
+        <item x="1025"/>
+        <item x="1026"/>
+        <item x="1027"/>
+        <item x="1028"/>
+        <item x="102"/>
+        <item x="1029"/>
+        <item x="1030"/>
+        <item x="1031"/>
+        <item x="1032"/>
+        <item x="1033"/>
+        <item x="1034"/>
+        <item x="1035"/>
+        <item x="1036"/>
+        <item x="1037"/>
+        <item x="1038"/>
+        <item x="103"/>
+        <item x="1039"/>
+        <item x="1040"/>
+        <item x="1041"/>
+        <item x="1042"/>
+        <item x="1043"/>
+        <item x="1044"/>
+        <item x="1045"/>
+        <item x="1046"/>
+        <item x="1047"/>
+        <item x="1048"/>
+        <item x="104"/>
+        <item x="1049"/>
+        <item x="1050"/>
+        <item x="1051"/>
+        <item x="1052"/>
+        <item x="1053"/>
+        <item x="1054"/>
+        <item x="1055"/>
+        <item x="1056"/>
+        <item x="1057"/>
+        <item x="1058"/>
+        <item x="105"/>
+        <item x="1059"/>
+        <item x="1060"/>
+        <item x="1061"/>
+        <item x="1062"/>
+        <item x="1063"/>
+        <item x="1064"/>
+        <item x="1065"/>
+        <item x="1066"/>
+        <item x="1067"/>
+        <item x="1068"/>
+        <item x="106"/>
+        <item x="1069"/>
+        <item x="1070"/>
+        <item x="1071"/>
+        <item x="1072"/>
+        <item x="1073"/>
+        <item x="1074"/>
+        <item x="1075"/>
+        <item x="1076"/>
+        <item x="1077"/>
+        <item x="1078"/>
+        <item x="107"/>
+        <item x="1079"/>
+        <item x="1080"/>
+        <item x="1081"/>
+        <item x="1082"/>
+        <item x="1083"/>
+        <item x="1084"/>
+        <item x="1085"/>
+        <item x="1086"/>
+        <item x="1087"/>
+        <item x="1088"/>
+        <item x="108"/>
+        <item x="1089"/>
+        <item x="1090"/>
+        <item x="1091"/>
+        <item x="1092"/>
+        <item x="1093"/>
+        <item x="1094"/>
+        <item x="1095"/>
+        <item x="1096"/>
+        <item x="1097"/>
+        <item x="1098"/>
+        <item x="10"/>
+        <item x="109"/>
+        <item x="1099"/>
+        <item x="1100"/>
+        <item x="1101"/>
+        <item x="1102"/>
+        <item x="1103"/>
+        <item x="1104"/>
+        <item x="1105"/>
+        <item x="1106"/>
+        <item x="1107"/>
+        <item x="1108"/>
+        <item x="110"/>
+        <item x="1109"/>
+        <item x="1110"/>
+        <item x="1111"/>
+        <item x="1112"/>
+        <item x="1113"/>
+        <item x="1114"/>
+        <item x="1115"/>
+        <item x="1116"/>
+        <item x="1117"/>
+        <item x="1118"/>
+        <item x="111"/>
+        <item x="1119"/>
+        <item x="1120"/>
+        <item x="1121"/>
+        <item x="1122"/>
+        <item x="1123"/>
+        <item x="1124"/>
+        <item x="1125"/>
+        <item x="1126"/>
+        <item x="1127"/>
+        <item x="1128"/>
+        <item x="112"/>
+        <item x="1129"/>
+        <item x="1130"/>
+        <item x="1131"/>
+        <item x="1132"/>
+        <item x="1133"/>
+        <item x="1134"/>
+        <item x="1135"/>
+        <item x="1136"/>
+        <item x="1137"/>
+        <item x="1138"/>
+        <item x="113"/>
+        <item x="1139"/>
+        <item x="1140"/>
+        <item x="1141"/>
+        <item x="1142"/>
+        <item x="1143"/>
+        <item x="1144"/>
+        <item x="1145"/>
+        <item x="1146"/>
+        <item x="1147"/>
+        <item x="1148"/>
+        <item x="114"/>
+        <item x="1149"/>
+        <item x="1150"/>
+        <item x="1151"/>
+        <item x="1152"/>
+        <item x="1153"/>
+        <item x="1154"/>
+        <item x="1155"/>
+        <item x="1156"/>
+        <item x="1157"/>
+        <item x="1158"/>
+        <item x="115"/>
+        <item x="1159"/>
+        <item x="1160"/>
+        <item x="1161"/>
+        <item x="1162"/>
+        <item x="1163"/>
+        <item x="1164"/>
+        <item x="1165"/>
+        <item x="1166"/>
+        <item x="1167"/>
+        <item x="1168"/>
+        <item x="116"/>
+        <item x="1169"/>
+        <item x="1170"/>
+        <item x="1171"/>
+        <item x="1172"/>
+        <item x="1173"/>
+        <item x="1174"/>
+        <item x="1175"/>
+        <item x="1176"/>
+        <item x="1177"/>
+        <item x="1178"/>
+        <item x="117"/>
+        <item x="1179"/>
+        <item x="1180"/>
+        <item x="1181"/>
+        <item x="1182"/>
+        <item x="1183"/>
+        <item x="1184"/>
+        <item x="1185"/>
+        <item x="1186"/>
+        <item x="1187"/>
+        <item x="1188"/>
+        <item x="118"/>
+        <item x="1189"/>
+        <item x="1190"/>
+        <item x="1191"/>
+        <item x="1192"/>
+        <item x="1193"/>
+        <item x="1194"/>
+        <item x="1195"/>
+        <item x="1196"/>
+        <item x="1197"/>
+        <item x="1198"/>
+        <item x="11"/>
+        <item x="119"/>
+        <item x="1199"/>
+        <item x="1200"/>
+        <item x="1201"/>
+        <item x="1202"/>
+        <item x="1203"/>
+        <item x="1204"/>
+        <item x="1205"/>
+        <item x="1206"/>
+        <item x="1207"/>
+        <item x="1208"/>
+        <item x="120"/>
+        <item x="1209"/>
+        <item x="1210"/>
+        <item x="1211"/>
+        <item x="1212"/>
+        <item x="1213"/>
+        <item x="1214"/>
+        <item x="1215"/>
+        <item x="1216"/>
+        <item x="1217"/>
+        <item x="1218"/>
+        <item x="121"/>
+        <item x="1219"/>
+        <item x="1220"/>
+        <item x="1221"/>
+        <item x="1222"/>
+        <item x="1223"/>
+        <item x="1224"/>
+        <item x="1225"/>
+        <item x="1226"/>
+        <item x="1227"/>
+        <item x="1228"/>
+        <item x="122"/>
+        <item x="1229"/>
+        <item x="1230"/>
+        <item x="1231"/>
+        <item x="1232"/>
+        <item x="1233"/>
+        <item x="1234"/>
+        <item x="1235"/>
+        <item x="1236"/>
+        <item x="1237"/>
+        <item x="1238"/>
+        <item x="123"/>
+        <item x="1239"/>
+        <item x="1240"/>
+        <item x="1241"/>
+        <item x="1242"/>
+        <item x="1243"/>
+        <item x="1244"/>
+        <item x="1245"/>
+        <item x="1246"/>
+        <item x="1247"/>
+        <item x="1248"/>
+        <item x="124"/>
+        <item x="1249"/>
+        <item x="1250"/>
+        <item x="1251"/>
+        <item x="1252"/>
+        <item x="1253"/>
+        <item x="1254"/>
+        <item x="1255"/>
+        <item x="1256"/>
+        <item x="1257"/>
+        <item x="1258"/>
+        <item x="125"/>
+        <item x="1259"/>
+        <item x="1260"/>
+        <item x="1261"/>
+        <item x="1262"/>
+        <item x="1263"/>
+        <item x="1264"/>
+        <item x="1265"/>
+        <item x="1266"/>
+        <item x="1267"/>
+        <item x="1268"/>
+        <item x="126"/>
+        <item x="1269"/>
+        <item x="1270"/>
+        <item x="1271"/>
+        <item x="1272"/>
+        <item x="1273"/>
+        <item x="1274"/>
+        <item x="1275"/>
+        <item x="1276"/>
+        <item x="1277"/>
+        <item x="1278"/>
+        <item x="127"/>
+        <item x="1279"/>
+        <item x="1280"/>
+        <item x="1281"/>
+        <item x="1282"/>
+        <item x="1283"/>
+        <item x="1284"/>
+        <item x="1285"/>
+        <item x="1286"/>
+        <item x="1287"/>
+        <item x="1288"/>
+        <item x="128"/>
+        <item x="1289"/>
+        <item x="1290"/>
+        <item x="1291"/>
+        <item x="1292"/>
+        <item x="1293"/>
+        <item x="1294"/>
+        <item x="1295"/>
+        <item x="1296"/>
+        <item x="1297"/>
+        <item x="1298"/>
+        <item x="12"/>
+        <item x="129"/>
+        <item x="1299"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="13"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="14"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="15"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="16"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="17"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="18"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="20"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="21"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="22"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="23"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="24"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="25"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="26"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="27"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="28"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="30"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="31"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="32"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="33"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="34"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="35"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="36"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="37"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="38"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="3"/>
+        <item x="39"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="40"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="41"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="42"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="43"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="44"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="45"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="46"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="47"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="48"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item x="4"/>
+        <item x="49"/>
+        <item x="499"/>
+        <item x="500"/>
+        <item x="501"/>
+        <item x="502"/>
+        <item x="503"/>
+        <item x="504"/>
+        <item x="505"/>
+        <item x="506"/>
+        <item x="507"/>
+        <item x="508"/>
+        <item x="50"/>
+        <item x="509"/>
+        <item x="510"/>
+        <item x="511"/>
+        <item x="512"/>
+        <item x="513"/>
+        <item x="514"/>
+        <item x="515"/>
+        <item x="516"/>
+        <item x="517"/>
+        <item x="518"/>
+        <item x="51"/>
+        <item x="519"/>
+        <item x="520"/>
+        <item x="521"/>
+        <item x="522"/>
+        <item x="523"/>
+        <item x="524"/>
+        <item x="525"/>
+        <item x="526"/>
+        <item x="527"/>
+        <item x="528"/>
+        <item x="52"/>
+        <item x="529"/>
+        <item x="530"/>
+        <item x="531"/>
+        <item x="532"/>
+        <item x="533"/>
+        <item x="534"/>
+        <item x="535"/>
+        <item x="536"/>
+        <item x="537"/>
+        <item x="538"/>
+        <item x="53"/>
+        <item x="539"/>
+        <item x="540"/>
+        <item x="541"/>
+        <item x="542"/>
+        <item x="543"/>
+        <item x="544"/>
+        <item x="545"/>
+        <item x="546"/>
+        <item x="547"/>
+        <item x="548"/>
+        <item x="54"/>
+        <item x="549"/>
+        <item x="550"/>
+        <item x="551"/>
+        <item x="552"/>
+        <item x="553"/>
+        <item x="554"/>
+        <item x="555"/>
+        <item x="556"/>
+        <item x="557"/>
+        <item x="558"/>
+        <item x="55"/>
+        <item x="559"/>
+        <item x="560"/>
+        <item x="561"/>
+        <item x="562"/>
+        <item x="563"/>
+        <item x="564"/>
+        <item x="565"/>
+        <item x="566"/>
+        <item x="567"/>
+        <item x="568"/>
+        <item x="56"/>
+        <item x="569"/>
+        <item x="570"/>
+        <item x="571"/>
+        <item x="572"/>
+        <item x="573"/>
+        <item x="574"/>
+        <item x="575"/>
+        <item x="576"/>
+        <item x="577"/>
+        <item x="578"/>
+        <item x="57"/>
+        <item x="579"/>
+        <item x="580"/>
+        <item x="581"/>
+        <item x="582"/>
+        <item x="583"/>
+        <item x="584"/>
+        <item x="585"/>
+        <item x="586"/>
+        <item x="587"/>
+        <item x="588"/>
+        <item x="58"/>
+        <item x="589"/>
+        <item x="590"/>
+        <item x="591"/>
+        <item x="592"/>
+        <item x="593"/>
+        <item x="594"/>
+        <item x="595"/>
+        <item x="596"/>
+        <item x="597"/>
+        <item x="598"/>
+        <item x="5"/>
+        <item x="59"/>
+        <item x="599"/>
+        <item x="600"/>
+        <item x="601"/>
+        <item x="602"/>
+        <item x="603"/>
+        <item x="604"/>
+        <item x="605"/>
+        <item x="606"/>
+        <item x="607"/>
+        <item x="608"/>
+        <item x="60"/>
+        <item x="609"/>
+        <item x="610"/>
+        <item x="611"/>
+        <item x="612"/>
+        <item x="613"/>
+        <item x="614"/>
+        <item x="615"/>
+        <item x="616"/>
+        <item x="617"/>
+        <item x="618"/>
+        <item x="61"/>
+        <item x="619"/>
+        <item x="620"/>
+        <item x="621"/>
+        <item x="622"/>
+        <item x="623"/>
+        <item x="624"/>
+        <item x="625"/>
+        <item x="626"/>
+        <item x="627"/>
+        <item x="628"/>
+        <item x="62"/>
+        <item x="629"/>
+        <item x="630"/>
+        <item x="631"/>
+        <item x="632"/>
+        <item x="633"/>
+        <item x="634"/>
+        <item x="635"/>
+        <item x="636"/>
+        <item x="637"/>
+        <item x="638"/>
+        <item x="63"/>
+        <item x="639"/>
+        <item x="640"/>
+        <item x="641"/>
+        <item x="642"/>
+        <item x="643"/>
+        <item x="644"/>
+        <item x="645"/>
+        <item x="646"/>
+        <item x="647"/>
+        <item x="648"/>
+        <item x="64"/>
+        <item x="649"/>
+        <item x="650"/>
+        <item x="651"/>
+        <item x="652"/>
+        <item x="653"/>
+        <item x="654"/>
+        <item x="655"/>
+        <item x="656"/>
+        <item x="657"/>
+        <item x="658"/>
+        <item x="65"/>
+        <item x="659"/>
+        <item x="660"/>
+        <item x="661"/>
+        <item x="662"/>
+        <item x="663"/>
+        <item x="664"/>
+        <item x="665"/>
+        <item x="666"/>
+        <item x="667"/>
+        <item x="668"/>
+        <item x="66"/>
+        <item x="669"/>
+        <item x="670"/>
+        <item x="671"/>
+        <item x="672"/>
+        <item x="673"/>
+        <item x="674"/>
+        <item x="675"/>
+        <item x="676"/>
+        <item x="677"/>
+        <item x="678"/>
+        <item x="67"/>
+        <item x="679"/>
+        <item x="680"/>
+        <item x="681"/>
+        <item x="682"/>
+        <item x="683"/>
+        <item x="684"/>
+        <item x="685"/>
+        <item x="686"/>
+        <item x="687"/>
+        <item x="688"/>
+        <item x="68"/>
+        <item x="689"/>
+        <item x="690"/>
+        <item x="691"/>
+        <item x="692"/>
+        <item x="693"/>
+        <item x="694"/>
+        <item x="695"/>
+        <item x="696"/>
+        <item x="697"/>
+        <item x="698"/>
+        <item x="6"/>
+        <item x="69"/>
+        <item x="699"/>
+        <item x="700"/>
+        <item x="701"/>
+        <item x="702"/>
+        <item x="703"/>
+        <item x="704"/>
+        <item x="705"/>
+        <item x="706"/>
+        <item x="707"/>
+        <item x="708"/>
+        <item x="70"/>
+        <item x="709"/>
+        <item x="710"/>
+        <item x="711"/>
+        <item x="712"/>
+        <item x="713"/>
+        <item x="714"/>
+        <item x="715"/>
+        <item x="716"/>
+        <item x="717"/>
+        <item x="718"/>
+        <item x="71"/>
+        <item x="719"/>
+        <item x="720"/>
+        <item x="721"/>
+        <item x="722"/>
+        <item x="723"/>
+        <item x="724"/>
+        <item x="725"/>
+        <item x="726"/>
+        <item x="727"/>
+        <item x="728"/>
+        <item x="72"/>
+        <item x="729"/>
+        <item x="730"/>
+        <item x="731"/>
+        <item x="732"/>
+        <item x="733"/>
+        <item x="734"/>
+        <item x="735"/>
+        <item x="736"/>
+        <item x="737"/>
+        <item x="738"/>
+        <item x="73"/>
+        <item x="739"/>
+        <item x="740"/>
+        <item x="741"/>
+        <item x="742"/>
+        <item x="743"/>
+        <item x="744"/>
+        <item x="745"/>
+        <item x="746"/>
+        <item x="747"/>
+        <item x="748"/>
+        <item x="74"/>
+        <item x="749"/>
+        <item x="750"/>
+        <item x="751"/>
+        <item x="752"/>
+        <item x="753"/>
+        <item x="754"/>
+        <item x="755"/>
+        <item x="756"/>
+        <item x="757"/>
+        <item x="758"/>
+        <item x="75"/>
+        <item x="759"/>
+        <item x="760"/>
+        <item x="761"/>
+        <item x="762"/>
+        <item x="763"/>
+        <item x="764"/>
+        <item x="765"/>
+        <item x="766"/>
+        <item x="767"/>
+        <item x="768"/>
+        <item x="76"/>
+        <item x="769"/>
+        <item x="770"/>
+        <item x="771"/>
+        <item x="772"/>
+        <item x="773"/>
+        <item x="774"/>
+        <item x="775"/>
+        <item x="776"/>
+        <item x="777"/>
+        <item x="778"/>
+        <item x="77"/>
+        <item x="779"/>
+        <item x="780"/>
+        <item x="781"/>
+        <item x="782"/>
+        <item x="783"/>
+        <item x="784"/>
+        <item x="785"/>
+        <item x="786"/>
+        <item x="787"/>
+        <item x="788"/>
+        <item x="78"/>
+        <item x="789"/>
+        <item x="790"/>
+        <item x="791"/>
+        <item x="792"/>
+        <item x="793"/>
+        <item x="794"/>
+        <item x="795"/>
+        <item x="796"/>
+        <item x="797"/>
+        <item x="798"/>
+        <item x="7"/>
+        <item x="79"/>
+        <item x="799"/>
+        <item x="800"/>
+        <item x="801"/>
+        <item x="802"/>
+        <item x="803"/>
+        <item x="804"/>
+        <item x="805"/>
+        <item x="806"/>
+        <item x="807"/>
+        <item x="808"/>
+        <item x="80"/>
+        <item x="809"/>
+        <item x="810"/>
+        <item x="811"/>
+        <item x="812"/>
+        <item x="813"/>
+        <item x="814"/>
+        <item x="815"/>
+        <item x="816"/>
+        <item x="817"/>
+        <item x="818"/>
+        <item x="81"/>
+        <item x="819"/>
+        <item x="820"/>
+        <item x="821"/>
+        <item x="822"/>
+        <item x="823"/>
+        <item x="824"/>
+        <item x="825"/>
+        <item x="826"/>
+        <item x="827"/>
+        <item x="828"/>
+        <item x="82"/>
+        <item x="829"/>
+        <item x="830"/>
+        <item x="831"/>
+        <item x="832"/>
+        <item x="833"/>
+        <item x="834"/>
+        <item x="835"/>
+        <item x="836"/>
+        <item x="837"/>
+        <item x="838"/>
+        <item x="83"/>
+        <item x="839"/>
+        <item x="840"/>
+        <item x="841"/>
+        <item x="842"/>
+        <item x="843"/>
+        <item x="844"/>
+        <item x="845"/>
+        <item x="846"/>
+        <item x="847"/>
+        <item x="848"/>
+        <item x="84"/>
+        <item x="849"/>
+        <item x="850"/>
+        <item x="851"/>
+        <item x="852"/>
+        <item x="853"/>
+        <item x="854"/>
+        <item x="855"/>
+        <item x="856"/>
+        <item x="857"/>
+        <item x="858"/>
+        <item x="85"/>
+        <item x="859"/>
+        <item x="860"/>
+        <item x="861"/>
+        <item x="862"/>
+        <item x="863"/>
+        <item x="864"/>
+        <item x="865"/>
+        <item x="866"/>
+        <item x="867"/>
+        <item x="868"/>
+        <item x="86"/>
+        <item x="869"/>
+        <item x="870"/>
+        <item x="871"/>
+        <item x="872"/>
+        <item x="873"/>
+        <item x="874"/>
+        <item x="875"/>
+        <item x="876"/>
+        <item x="877"/>
+        <item x="878"/>
+        <item x="87"/>
+        <item x="879"/>
+        <item x="880"/>
+        <item x="881"/>
+        <item x="882"/>
+        <item x="883"/>
+        <item x="884"/>
+        <item x="885"/>
+        <item x="886"/>
+        <item x="887"/>
+        <item x="888"/>
+        <item x="88"/>
+        <item x="889"/>
+        <item x="890"/>
+        <item x="891"/>
+        <item x="892"/>
+        <item x="893"/>
+        <item x="894"/>
+        <item x="895"/>
+        <item x="896"/>
+        <item x="897"/>
+        <item x="898"/>
+        <item x="8"/>
+        <item x="89"/>
+        <item x="899"/>
+        <item x="900"/>
+        <item x="901"/>
+        <item x="902"/>
+        <item x="903"/>
+        <item x="904"/>
+        <item x="905"/>
+        <item x="906"/>
+        <item x="907"/>
+        <item x="908"/>
+        <item x="90"/>
+        <item x="909"/>
+        <item x="910"/>
+        <item x="911"/>
+        <item x="912"/>
+        <item x="913"/>
+        <item x="914"/>
+        <item x="915"/>
+        <item x="916"/>
+        <item x="917"/>
+        <item x="918"/>
+        <item x="91"/>
+        <item x="919"/>
+        <item x="920"/>
+        <item x="921"/>
+        <item x="922"/>
+        <item x="923"/>
+        <item x="924"/>
+        <item x="925"/>
+        <item x="926"/>
+        <item x="927"/>
+        <item x="928"/>
+        <item x="92"/>
+        <item x="929"/>
+        <item x="930"/>
+        <item x="931"/>
+        <item x="932"/>
+        <item x="933"/>
+        <item x="934"/>
+        <item x="935"/>
+        <item x="936"/>
+        <item x="937"/>
+        <item x="938"/>
+        <item x="93"/>
+        <item x="939"/>
+        <item x="940"/>
+        <item x="941"/>
+        <item x="942"/>
+        <item x="943"/>
+        <item x="944"/>
+        <item x="945"/>
+        <item x="946"/>
+        <item x="947"/>
+        <item x="948"/>
+        <item x="94"/>
+        <item x="949"/>
+        <item x="950"/>
+        <item x="951"/>
+        <item x="952"/>
+        <item x="953"/>
+        <item x="954"/>
+        <item x="955"/>
+        <item x="956"/>
+        <item x="957"/>
+        <item x="958"/>
+        <item x="95"/>
+        <item x="959"/>
+        <item x="960"/>
+        <item x="961"/>
+        <item x="962"/>
+        <item x="963"/>
+        <item x="964"/>
+        <item x="965"/>
+        <item x="966"/>
+        <item x="967"/>
+        <item x="968"/>
+        <item x="96"/>
+        <item x="969"/>
+        <item x="970"/>
+        <item x="971"/>
+        <item x="972"/>
+        <item x="973"/>
+        <item x="974"/>
+        <item x="975"/>
+        <item x="976"/>
+        <item x="977"/>
+        <item x="978"/>
+        <item x="97"/>
+        <item x="979"/>
+        <item x="980"/>
+        <item x="981"/>
+        <item x="982"/>
+        <item x="983"/>
+        <item x="984"/>
+        <item x="985"/>
+        <item x="986"/>
+        <item x="987"/>
+        <item x="988"/>
+        <item x="98"/>
+        <item x="989"/>
+        <item x="990"/>
+        <item x="991"/>
+        <item x="992"/>
+        <item x="993"/>
+        <item x="994"/>
+        <item x="995"/>
+        <item x="996"/>
+        <item x="997"/>
+        <item x="998"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="32">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total commission" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="32">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0324B6A6-8E31-4843-B69E-3CBA9D29CB07}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A7:A8" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -44166,31 +42659,1391 @@
     <dataField name="Total Sales " fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="105">
+    <format dxfId="41">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="104">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="103">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="102">
+    <format dxfId="38">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="101">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="100">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="98">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="97">
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68D9E7EF-3B4D-4F92-A5BE-1179E186F699}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="10">
+    <pivotField showAll="0">
+      <items count="1301">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="99"/>
+        <item x="999"/>
+        <item x="1000"/>
+        <item x="1001"/>
+        <item x="1002"/>
+        <item x="1003"/>
+        <item x="1004"/>
+        <item x="1005"/>
+        <item x="1006"/>
+        <item x="1007"/>
+        <item x="1008"/>
+        <item x="100"/>
+        <item x="1009"/>
+        <item x="1010"/>
+        <item x="1011"/>
+        <item x="1012"/>
+        <item x="1013"/>
+        <item x="1014"/>
+        <item x="1015"/>
+        <item x="1016"/>
+        <item x="1017"/>
+        <item x="1018"/>
+        <item x="101"/>
+        <item x="1019"/>
+        <item x="1020"/>
+        <item x="1021"/>
+        <item x="1022"/>
+        <item x="1023"/>
+        <item x="1024"/>
+        <item x="1025"/>
+        <item x="1026"/>
+        <item x="1027"/>
+        <item x="1028"/>
+        <item x="102"/>
+        <item x="1029"/>
+        <item x="1030"/>
+        <item x="1031"/>
+        <item x="1032"/>
+        <item x="1033"/>
+        <item x="1034"/>
+        <item x="1035"/>
+        <item x="1036"/>
+        <item x="1037"/>
+        <item x="1038"/>
+        <item x="103"/>
+        <item x="1039"/>
+        <item x="1040"/>
+        <item x="1041"/>
+        <item x="1042"/>
+        <item x="1043"/>
+        <item x="1044"/>
+        <item x="1045"/>
+        <item x="1046"/>
+        <item x="1047"/>
+        <item x="1048"/>
+        <item x="104"/>
+        <item x="1049"/>
+        <item x="1050"/>
+        <item x="1051"/>
+        <item x="1052"/>
+        <item x="1053"/>
+        <item x="1054"/>
+        <item x="1055"/>
+        <item x="1056"/>
+        <item x="1057"/>
+        <item x="1058"/>
+        <item x="105"/>
+        <item x="1059"/>
+        <item x="1060"/>
+        <item x="1061"/>
+        <item x="1062"/>
+        <item x="1063"/>
+        <item x="1064"/>
+        <item x="1065"/>
+        <item x="1066"/>
+        <item x="1067"/>
+        <item x="1068"/>
+        <item x="106"/>
+        <item x="1069"/>
+        <item x="1070"/>
+        <item x="1071"/>
+        <item x="1072"/>
+        <item x="1073"/>
+        <item x="1074"/>
+        <item x="1075"/>
+        <item x="1076"/>
+        <item x="1077"/>
+        <item x="1078"/>
+        <item x="107"/>
+        <item x="1079"/>
+        <item x="1080"/>
+        <item x="1081"/>
+        <item x="1082"/>
+        <item x="1083"/>
+        <item x="1084"/>
+        <item x="1085"/>
+        <item x="1086"/>
+        <item x="1087"/>
+        <item x="1088"/>
+        <item x="108"/>
+        <item x="1089"/>
+        <item x="1090"/>
+        <item x="1091"/>
+        <item x="1092"/>
+        <item x="1093"/>
+        <item x="1094"/>
+        <item x="1095"/>
+        <item x="1096"/>
+        <item x="1097"/>
+        <item x="1098"/>
+        <item x="10"/>
+        <item x="109"/>
+        <item x="1099"/>
+        <item x="1100"/>
+        <item x="1101"/>
+        <item x="1102"/>
+        <item x="1103"/>
+        <item x="1104"/>
+        <item x="1105"/>
+        <item x="1106"/>
+        <item x="1107"/>
+        <item x="1108"/>
+        <item x="110"/>
+        <item x="1109"/>
+        <item x="1110"/>
+        <item x="1111"/>
+        <item x="1112"/>
+        <item x="1113"/>
+        <item x="1114"/>
+        <item x="1115"/>
+        <item x="1116"/>
+        <item x="1117"/>
+        <item x="1118"/>
+        <item x="111"/>
+        <item x="1119"/>
+        <item x="1120"/>
+        <item x="1121"/>
+        <item x="1122"/>
+        <item x="1123"/>
+        <item x="1124"/>
+        <item x="1125"/>
+        <item x="1126"/>
+        <item x="1127"/>
+        <item x="1128"/>
+        <item x="112"/>
+        <item x="1129"/>
+        <item x="1130"/>
+        <item x="1131"/>
+        <item x="1132"/>
+        <item x="1133"/>
+        <item x="1134"/>
+        <item x="1135"/>
+        <item x="1136"/>
+        <item x="1137"/>
+        <item x="1138"/>
+        <item x="113"/>
+        <item x="1139"/>
+        <item x="1140"/>
+        <item x="1141"/>
+        <item x="1142"/>
+        <item x="1143"/>
+        <item x="1144"/>
+        <item x="1145"/>
+        <item x="1146"/>
+        <item x="1147"/>
+        <item x="1148"/>
+        <item x="114"/>
+        <item x="1149"/>
+        <item x="1150"/>
+        <item x="1151"/>
+        <item x="1152"/>
+        <item x="1153"/>
+        <item x="1154"/>
+        <item x="1155"/>
+        <item x="1156"/>
+        <item x="1157"/>
+        <item x="1158"/>
+        <item x="115"/>
+        <item x="1159"/>
+        <item x="1160"/>
+        <item x="1161"/>
+        <item x="1162"/>
+        <item x="1163"/>
+        <item x="1164"/>
+        <item x="1165"/>
+        <item x="1166"/>
+        <item x="1167"/>
+        <item x="1168"/>
+        <item x="116"/>
+        <item x="1169"/>
+        <item x="1170"/>
+        <item x="1171"/>
+        <item x="1172"/>
+        <item x="1173"/>
+        <item x="1174"/>
+        <item x="1175"/>
+        <item x="1176"/>
+        <item x="1177"/>
+        <item x="1178"/>
+        <item x="117"/>
+        <item x="1179"/>
+        <item x="1180"/>
+        <item x="1181"/>
+        <item x="1182"/>
+        <item x="1183"/>
+        <item x="1184"/>
+        <item x="1185"/>
+        <item x="1186"/>
+        <item x="1187"/>
+        <item x="1188"/>
+        <item x="118"/>
+        <item x="1189"/>
+        <item x="1190"/>
+        <item x="1191"/>
+        <item x="1192"/>
+        <item x="1193"/>
+        <item x="1194"/>
+        <item x="1195"/>
+        <item x="1196"/>
+        <item x="1197"/>
+        <item x="1198"/>
+        <item x="11"/>
+        <item x="119"/>
+        <item x="1199"/>
+        <item x="1200"/>
+        <item x="1201"/>
+        <item x="1202"/>
+        <item x="1203"/>
+        <item x="1204"/>
+        <item x="1205"/>
+        <item x="1206"/>
+        <item x="1207"/>
+        <item x="1208"/>
+        <item x="120"/>
+        <item x="1209"/>
+        <item x="1210"/>
+        <item x="1211"/>
+        <item x="1212"/>
+        <item x="1213"/>
+        <item x="1214"/>
+        <item x="1215"/>
+        <item x="1216"/>
+        <item x="1217"/>
+        <item x="1218"/>
+        <item x="121"/>
+        <item x="1219"/>
+        <item x="1220"/>
+        <item x="1221"/>
+        <item x="1222"/>
+        <item x="1223"/>
+        <item x="1224"/>
+        <item x="1225"/>
+        <item x="1226"/>
+        <item x="1227"/>
+        <item x="1228"/>
+        <item x="122"/>
+        <item x="1229"/>
+        <item x="1230"/>
+        <item x="1231"/>
+        <item x="1232"/>
+        <item x="1233"/>
+        <item x="1234"/>
+        <item x="1235"/>
+        <item x="1236"/>
+        <item x="1237"/>
+        <item x="1238"/>
+        <item x="123"/>
+        <item x="1239"/>
+        <item x="1240"/>
+        <item x="1241"/>
+        <item x="1242"/>
+        <item x="1243"/>
+        <item x="1244"/>
+        <item x="1245"/>
+        <item x="1246"/>
+        <item x="1247"/>
+        <item x="1248"/>
+        <item x="124"/>
+        <item x="1249"/>
+        <item x="1250"/>
+        <item x="1251"/>
+        <item x="1252"/>
+        <item x="1253"/>
+        <item x="1254"/>
+        <item x="1255"/>
+        <item x="1256"/>
+        <item x="1257"/>
+        <item x="1258"/>
+        <item x="125"/>
+        <item x="1259"/>
+        <item x="1260"/>
+        <item x="1261"/>
+        <item x="1262"/>
+        <item x="1263"/>
+        <item x="1264"/>
+        <item x="1265"/>
+        <item x="1266"/>
+        <item x="1267"/>
+        <item x="1268"/>
+        <item x="126"/>
+        <item x="1269"/>
+        <item x="1270"/>
+        <item x="1271"/>
+        <item x="1272"/>
+        <item x="1273"/>
+        <item x="1274"/>
+        <item x="1275"/>
+        <item x="1276"/>
+        <item x="1277"/>
+        <item x="1278"/>
+        <item x="127"/>
+        <item x="1279"/>
+        <item x="1280"/>
+        <item x="1281"/>
+        <item x="1282"/>
+        <item x="1283"/>
+        <item x="1284"/>
+        <item x="1285"/>
+        <item x="1286"/>
+        <item x="1287"/>
+        <item x="1288"/>
+        <item x="128"/>
+        <item x="1289"/>
+        <item x="1290"/>
+        <item x="1291"/>
+        <item x="1292"/>
+        <item x="1293"/>
+        <item x="1294"/>
+        <item x="1295"/>
+        <item x="1296"/>
+        <item x="1297"/>
+        <item x="1298"/>
+        <item x="12"/>
+        <item x="129"/>
+        <item x="1299"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="13"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="14"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="15"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="16"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="17"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="18"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="20"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="21"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="22"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="23"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="24"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="25"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="26"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="27"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="28"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="2"/>
+        <item x="29"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="30"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="31"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="32"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="33"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="34"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="35"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item x="368"/>
+        <item x="36"/>
+        <item x="369"/>
+        <item x="370"/>
+        <item x="371"/>
+        <item x="372"/>
+        <item x="373"/>
+        <item x="374"/>
+        <item x="375"/>
+        <item x="376"/>
+        <item x="377"/>
+        <item x="378"/>
+        <item x="37"/>
+        <item x="379"/>
+        <item x="380"/>
+        <item x="381"/>
+        <item x="382"/>
+        <item x="383"/>
+        <item x="384"/>
+        <item x="385"/>
+        <item x="386"/>
+        <item x="387"/>
+        <item x="388"/>
+        <item x="38"/>
+        <item x="389"/>
+        <item x="390"/>
+        <item x="391"/>
+        <item x="392"/>
+        <item x="393"/>
+        <item x="394"/>
+        <item x="395"/>
+        <item x="396"/>
+        <item x="397"/>
+        <item x="398"/>
+        <item x="3"/>
+        <item x="39"/>
+        <item x="399"/>
+        <item x="400"/>
+        <item x="401"/>
+        <item x="402"/>
+        <item x="403"/>
+        <item x="404"/>
+        <item x="405"/>
+        <item x="406"/>
+        <item x="407"/>
+        <item x="408"/>
+        <item x="40"/>
+        <item x="409"/>
+        <item x="410"/>
+        <item x="411"/>
+        <item x="412"/>
+        <item x="413"/>
+        <item x="414"/>
+        <item x="415"/>
+        <item x="416"/>
+        <item x="417"/>
+        <item x="418"/>
+        <item x="41"/>
+        <item x="419"/>
+        <item x="420"/>
+        <item x="421"/>
+        <item x="422"/>
+        <item x="423"/>
+        <item x="424"/>
+        <item x="425"/>
+        <item x="426"/>
+        <item x="427"/>
+        <item x="428"/>
+        <item x="42"/>
+        <item x="429"/>
+        <item x="430"/>
+        <item x="431"/>
+        <item x="432"/>
+        <item x="433"/>
+        <item x="434"/>
+        <item x="435"/>
+        <item x="436"/>
+        <item x="437"/>
+        <item x="438"/>
+        <item x="43"/>
+        <item x="439"/>
+        <item x="440"/>
+        <item x="441"/>
+        <item x="442"/>
+        <item x="443"/>
+        <item x="444"/>
+        <item x="445"/>
+        <item x="446"/>
+        <item x="447"/>
+        <item x="448"/>
+        <item x="44"/>
+        <item x="449"/>
+        <item x="450"/>
+        <item x="451"/>
+        <item x="452"/>
+        <item x="453"/>
+        <item x="454"/>
+        <item x="455"/>
+        <item x="456"/>
+        <item x="457"/>
+        <item x="458"/>
+        <item x="45"/>
+        <item x="459"/>
+        <item x="460"/>
+        <item x="461"/>
+        <item x="462"/>
+        <item x="463"/>
+        <item x="464"/>
+        <item x="465"/>
+        <item x="466"/>
+        <item x="467"/>
+        <item x="468"/>
+        <item x="46"/>
+        <item x="469"/>
+        <item x="470"/>
+        <item x="471"/>
+        <item x="472"/>
+        <item x="473"/>
+        <item x="474"/>
+        <item x="475"/>
+        <item x="476"/>
+        <item x="477"/>
+        <item x="478"/>
+        <item x="47"/>
+        <item x="479"/>
+        <item x="480"/>
+        <item x="481"/>
+        <item x="482"/>
+        <item x="483"/>
+        <item x="484"/>
+        <item x="485"/>
+        <item x="486"/>
+        <item x="487"/>
+        <item x="488"/>
+        <item x="48"/>
+        <item x="489"/>
+        <item x="490"/>
+        <item x="491"/>
+        <item x="492"/>
+        <item x="493"/>
+        <item x="494"/>
+        <item x="495"/>
+        <item x="496"/>
+        <item x="497"/>
+        <item x="498"/>
+        <item x="4"/>
+        <item x="49"/>
+        <item x="499"/>
+        <item x="500"/>
+        <item x="501"/>
+        <item x="502"/>
+        <item x="503"/>
+        <item x="504"/>
+        <item x="505"/>
+        <item x="506"/>
+        <item x="507"/>
+        <item x="508"/>
+        <item x="50"/>
+        <item x="509"/>
+        <item x="510"/>
+        <item x="511"/>
+        <item x="512"/>
+        <item x="513"/>
+        <item x="514"/>
+        <item x="515"/>
+        <item x="516"/>
+        <item x="517"/>
+        <item x="518"/>
+        <item x="51"/>
+        <item x="519"/>
+        <item x="520"/>
+        <item x="521"/>
+        <item x="522"/>
+        <item x="523"/>
+        <item x="524"/>
+        <item x="525"/>
+        <item x="526"/>
+        <item x="527"/>
+        <item x="528"/>
+        <item x="52"/>
+        <item x="529"/>
+        <item x="530"/>
+        <item x="531"/>
+        <item x="532"/>
+        <item x="533"/>
+        <item x="534"/>
+        <item x="535"/>
+        <item x="536"/>
+        <item x="537"/>
+        <item x="538"/>
+        <item x="53"/>
+        <item x="539"/>
+        <item x="540"/>
+        <item x="541"/>
+        <item x="542"/>
+        <item x="543"/>
+        <item x="544"/>
+        <item x="545"/>
+        <item x="546"/>
+        <item x="547"/>
+        <item x="548"/>
+        <item x="54"/>
+        <item x="549"/>
+        <item x="550"/>
+        <item x="551"/>
+        <item x="552"/>
+        <item x="553"/>
+        <item x="554"/>
+        <item x="555"/>
+        <item x="556"/>
+        <item x="557"/>
+        <item x="558"/>
+        <item x="55"/>
+        <item x="559"/>
+        <item x="560"/>
+        <item x="561"/>
+        <item x="562"/>
+        <item x="563"/>
+        <item x="564"/>
+        <item x="565"/>
+        <item x="566"/>
+        <item x="567"/>
+        <item x="568"/>
+        <item x="56"/>
+        <item x="569"/>
+        <item x="570"/>
+        <item x="571"/>
+        <item x="572"/>
+        <item x="573"/>
+        <item x="574"/>
+        <item x="575"/>
+        <item x="576"/>
+        <item x="577"/>
+        <item x="578"/>
+        <item x="57"/>
+        <item x="579"/>
+        <item x="580"/>
+        <item x="581"/>
+        <item x="582"/>
+        <item x="583"/>
+        <item x="584"/>
+        <item x="585"/>
+        <item x="586"/>
+        <item x="587"/>
+        <item x="588"/>
+        <item x="58"/>
+        <item x="589"/>
+        <item x="590"/>
+        <item x="591"/>
+        <item x="592"/>
+        <item x="593"/>
+        <item x="594"/>
+        <item x="595"/>
+        <item x="596"/>
+        <item x="597"/>
+        <item x="598"/>
+        <item x="5"/>
+        <item x="59"/>
+        <item x="599"/>
+        <item x="600"/>
+        <item x="601"/>
+        <item x="602"/>
+        <item x="603"/>
+        <item x="604"/>
+        <item x="605"/>
+        <item x="606"/>
+        <item x="607"/>
+        <item x="608"/>
+        <item x="60"/>
+        <item x="609"/>
+        <item x="610"/>
+        <item x="611"/>
+        <item x="612"/>
+        <item x="613"/>
+        <item x="614"/>
+        <item x="615"/>
+        <item x="616"/>
+        <item x="617"/>
+        <item x="618"/>
+        <item x="61"/>
+        <item x="619"/>
+        <item x="620"/>
+        <item x="621"/>
+        <item x="622"/>
+        <item x="623"/>
+        <item x="624"/>
+        <item x="625"/>
+        <item x="626"/>
+        <item x="627"/>
+        <item x="628"/>
+        <item x="62"/>
+        <item x="629"/>
+        <item x="630"/>
+        <item x="631"/>
+        <item x="632"/>
+        <item x="633"/>
+        <item x="634"/>
+        <item x="635"/>
+        <item x="636"/>
+        <item x="637"/>
+        <item x="638"/>
+        <item x="63"/>
+        <item x="639"/>
+        <item x="640"/>
+        <item x="641"/>
+        <item x="642"/>
+        <item x="643"/>
+        <item x="644"/>
+        <item x="645"/>
+        <item x="646"/>
+        <item x="647"/>
+        <item x="648"/>
+        <item x="64"/>
+        <item x="649"/>
+        <item x="650"/>
+        <item x="651"/>
+        <item x="652"/>
+        <item x="653"/>
+        <item x="654"/>
+        <item x="655"/>
+        <item x="656"/>
+        <item x="657"/>
+        <item x="658"/>
+        <item x="65"/>
+        <item x="659"/>
+        <item x="660"/>
+        <item x="661"/>
+        <item x="662"/>
+        <item x="663"/>
+        <item x="664"/>
+        <item x="665"/>
+        <item x="666"/>
+        <item x="667"/>
+        <item x="668"/>
+        <item x="66"/>
+        <item x="669"/>
+        <item x="670"/>
+        <item x="671"/>
+        <item x="672"/>
+        <item x="673"/>
+        <item x="674"/>
+        <item x="675"/>
+        <item x="676"/>
+        <item x="677"/>
+        <item x="678"/>
+        <item x="67"/>
+        <item x="679"/>
+        <item x="680"/>
+        <item x="681"/>
+        <item x="682"/>
+        <item x="683"/>
+        <item x="684"/>
+        <item x="685"/>
+        <item x="686"/>
+        <item x="687"/>
+        <item x="688"/>
+        <item x="68"/>
+        <item x="689"/>
+        <item x="690"/>
+        <item x="691"/>
+        <item x="692"/>
+        <item x="693"/>
+        <item x="694"/>
+        <item x="695"/>
+        <item x="696"/>
+        <item x="697"/>
+        <item x="698"/>
+        <item x="6"/>
+        <item x="69"/>
+        <item x="699"/>
+        <item x="700"/>
+        <item x="701"/>
+        <item x="702"/>
+        <item x="703"/>
+        <item x="704"/>
+        <item x="705"/>
+        <item x="706"/>
+        <item x="707"/>
+        <item x="708"/>
+        <item x="70"/>
+        <item x="709"/>
+        <item x="710"/>
+        <item x="711"/>
+        <item x="712"/>
+        <item x="713"/>
+        <item x="714"/>
+        <item x="715"/>
+        <item x="716"/>
+        <item x="717"/>
+        <item x="718"/>
+        <item x="71"/>
+        <item x="719"/>
+        <item x="720"/>
+        <item x="721"/>
+        <item x="722"/>
+        <item x="723"/>
+        <item x="724"/>
+        <item x="725"/>
+        <item x="726"/>
+        <item x="727"/>
+        <item x="728"/>
+        <item x="72"/>
+        <item x="729"/>
+        <item x="730"/>
+        <item x="731"/>
+        <item x="732"/>
+        <item x="733"/>
+        <item x="734"/>
+        <item x="735"/>
+        <item x="736"/>
+        <item x="737"/>
+        <item x="738"/>
+        <item x="73"/>
+        <item x="739"/>
+        <item x="740"/>
+        <item x="741"/>
+        <item x="742"/>
+        <item x="743"/>
+        <item x="744"/>
+        <item x="745"/>
+        <item x="746"/>
+        <item x="747"/>
+        <item x="748"/>
+        <item x="74"/>
+        <item x="749"/>
+        <item x="750"/>
+        <item x="751"/>
+        <item x="752"/>
+        <item x="753"/>
+        <item x="754"/>
+        <item x="755"/>
+        <item x="756"/>
+        <item x="757"/>
+        <item x="758"/>
+        <item x="75"/>
+        <item x="759"/>
+        <item x="760"/>
+        <item x="761"/>
+        <item x="762"/>
+        <item x="763"/>
+        <item x="764"/>
+        <item x="765"/>
+        <item x="766"/>
+        <item x="767"/>
+        <item x="768"/>
+        <item x="76"/>
+        <item x="769"/>
+        <item x="770"/>
+        <item x="771"/>
+        <item x="772"/>
+        <item x="773"/>
+        <item x="774"/>
+        <item x="775"/>
+        <item x="776"/>
+        <item x="777"/>
+        <item x="778"/>
+        <item x="77"/>
+        <item x="779"/>
+        <item x="780"/>
+        <item x="781"/>
+        <item x="782"/>
+        <item x="783"/>
+        <item x="784"/>
+        <item x="785"/>
+        <item x="786"/>
+        <item x="787"/>
+        <item x="788"/>
+        <item x="78"/>
+        <item x="789"/>
+        <item x="790"/>
+        <item x="791"/>
+        <item x="792"/>
+        <item x="793"/>
+        <item x="794"/>
+        <item x="795"/>
+        <item x="796"/>
+        <item x="797"/>
+        <item x="798"/>
+        <item x="7"/>
+        <item x="79"/>
+        <item x="799"/>
+        <item x="800"/>
+        <item x="801"/>
+        <item x="802"/>
+        <item x="803"/>
+        <item x="804"/>
+        <item x="805"/>
+        <item x="806"/>
+        <item x="807"/>
+        <item x="808"/>
+        <item x="80"/>
+        <item x="809"/>
+        <item x="810"/>
+        <item x="811"/>
+        <item x="812"/>
+        <item x="813"/>
+        <item x="814"/>
+        <item x="815"/>
+        <item x="816"/>
+        <item x="817"/>
+        <item x="818"/>
+        <item x="81"/>
+        <item x="819"/>
+        <item x="820"/>
+        <item x="821"/>
+        <item x="822"/>
+        <item x="823"/>
+        <item x="824"/>
+        <item x="825"/>
+        <item x="826"/>
+        <item x="827"/>
+        <item x="828"/>
+        <item x="82"/>
+        <item x="829"/>
+        <item x="830"/>
+        <item x="831"/>
+        <item x="832"/>
+        <item x="833"/>
+        <item x="834"/>
+        <item x="835"/>
+        <item x="836"/>
+        <item x="837"/>
+        <item x="838"/>
+        <item x="83"/>
+        <item x="839"/>
+        <item x="840"/>
+        <item x="841"/>
+        <item x="842"/>
+        <item x="843"/>
+        <item x="844"/>
+        <item x="845"/>
+        <item x="846"/>
+        <item x="847"/>
+        <item x="848"/>
+        <item x="84"/>
+        <item x="849"/>
+        <item x="850"/>
+        <item x="851"/>
+        <item x="852"/>
+        <item x="853"/>
+        <item x="854"/>
+        <item x="855"/>
+        <item x="856"/>
+        <item x="857"/>
+        <item x="858"/>
+        <item x="85"/>
+        <item x="859"/>
+        <item x="860"/>
+        <item x="861"/>
+        <item x="862"/>
+        <item x="863"/>
+        <item x="864"/>
+        <item x="865"/>
+        <item x="866"/>
+        <item x="867"/>
+        <item x="868"/>
+        <item x="86"/>
+        <item x="869"/>
+        <item x="870"/>
+        <item x="871"/>
+        <item x="872"/>
+        <item x="873"/>
+        <item x="874"/>
+        <item x="875"/>
+        <item x="876"/>
+        <item x="877"/>
+        <item x="878"/>
+        <item x="87"/>
+        <item x="879"/>
+        <item x="880"/>
+        <item x="881"/>
+        <item x="882"/>
+        <item x="883"/>
+        <item x="884"/>
+        <item x="885"/>
+        <item x="886"/>
+        <item x="887"/>
+        <item x="888"/>
+        <item x="88"/>
+        <item x="889"/>
+        <item x="890"/>
+        <item x="891"/>
+        <item x="892"/>
+        <item x="893"/>
+        <item x="894"/>
+        <item x="895"/>
+        <item x="896"/>
+        <item x="897"/>
+        <item x="898"/>
+        <item x="8"/>
+        <item x="89"/>
+        <item x="899"/>
+        <item x="900"/>
+        <item x="901"/>
+        <item x="902"/>
+        <item x="903"/>
+        <item x="904"/>
+        <item x="905"/>
+        <item x="906"/>
+        <item x="907"/>
+        <item x="908"/>
+        <item x="90"/>
+        <item x="909"/>
+        <item x="910"/>
+        <item x="911"/>
+        <item x="912"/>
+        <item x="913"/>
+        <item x="914"/>
+        <item x="915"/>
+        <item x="916"/>
+        <item x="917"/>
+        <item x="918"/>
+        <item x="91"/>
+        <item x="919"/>
+        <item x="920"/>
+        <item x="921"/>
+        <item x="922"/>
+        <item x="923"/>
+        <item x="924"/>
+        <item x="925"/>
+        <item x="926"/>
+        <item x="927"/>
+        <item x="928"/>
+        <item x="92"/>
+        <item x="929"/>
+        <item x="930"/>
+        <item x="931"/>
+        <item x="932"/>
+        <item x="933"/>
+        <item x="934"/>
+        <item x="935"/>
+        <item x="936"/>
+        <item x="937"/>
+        <item x="938"/>
+        <item x="93"/>
+        <item x="939"/>
+        <item x="940"/>
+        <item x="941"/>
+        <item x="942"/>
+        <item x="943"/>
+        <item x="944"/>
+        <item x="945"/>
+        <item x="946"/>
+        <item x="947"/>
+        <item x="948"/>
+        <item x="94"/>
+        <item x="949"/>
+        <item x="950"/>
+        <item x="951"/>
+        <item x="952"/>
+        <item x="953"/>
+        <item x="954"/>
+        <item x="955"/>
+        <item x="956"/>
+        <item x="957"/>
+        <item x="958"/>
+        <item x="95"/>
+        <item x="959"/>
+        <item x="960"/>
+        <item x="961"/>
+        <item x="962"/>
+        <item x="963"/>
+        <item x="964"/>
+        <item x="965"/>
+        <item x="966"/>
+        <item x="967"/>
+        <item x="968"/>
+        <item x="96"/>
+        <item x="969"/>
+        <item x="970"/>
+        <item x="971"/>
+        <item x="972"/>
+        <item x="973"/>
+        <item x="974"/>
+        <item x="975"/>
+        <item x="976"/>
+        <item x="977"/>
+        <item x="978"/>
+        <item x="97"/>
+        <item x="979"/>
+        <item x="980"/>
+        <item x="981"/>
+        <item x="982"/>
+        <item x="983"/>
+        <item x="984"/>
+        <item x="985"/>
+        <item x="986"/>
+        <item x="987"/>
+        <item x="988"/>
+        <item x="98"/>
+        <item x="989"/>
+        <item x="990"/>
+        <item x="991"/>
+        <item x="992"/>
+        <item x="993"/>
+        <item x="994"/>
+        <item x="995"/>
+        <item x="996"/>
+        <item x="997"/>
+        <item x="998"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total commissions" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="47">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="46">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="45">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -44207,7 +44060,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61FC0772-9B09-4F85-B0BA-A3A534BECD81}" name="PivotTable8" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61FC0772-9B09-4F85-B0BA-A3A534BECD81}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
   <location ref="A64:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -45608,22 +45461,22 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="111">
+    <format dxfId="53">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="109">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="108">
+    <format dxfId="50">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="107">
+    <format dxfId="49">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="106">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -45679,19 +45532,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{435F833D-F8DA-48DE-9202-B66D398C4EC4}" name="raw_data_one_month_sales_Report" displayName="raw_data_one_month_sales_Report" ref="A1:J1301" tableType="queryTable" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{435F833D-F8DA-48DE-9202-B66D398C4EC4}" name="raw_data_one_month_sales_Report" displayName="raw_data_one_month_sales_Report" ref="A1:J1301" tableType="queryTable" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <autoFilter ref="A1:J1301" xr:uid="{435F833D-F8DA-48DE-9202-B66D398C4EC4}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{2478EC7B-9201-464C-97D1-7832CCFDD2A3}" uniqueName="1" name="Order_Id" queryTableFieldId="1" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{02B1DDE7-04CB-444B-ABEF-B90EAE5BA784}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{3C227B4A-8B12-4E4A-8F27-1A3C59A8F10F}" uniqueName="3" name="Item" queryTableFieldId="3" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{54E1CEE4-3B48-4D5A-8DA9-63C555A7FFFA}" uniqueName="4" name="Sales Rep" queryTableFieldId="4" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{9EC9992A-CB31-468E-9F69-4C965DD568D7}" uniqueName="5" name="Quantity" queryTableFieldId="5" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{6BB9D655-1011-4F3B-970D-80AB6F3EFBD8}" uniqueName="6" name="Price" queryTableFieldId="6" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{90CEDEA1-E2DB-4335-AD05-BC1C207AA4FB}" uniqueName="7" name="Total Sales" queryTableFieldId="7" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{BB982F64-1660-4B4F-B68D-2475B8D84B45}" uniqueName="8" name="Commission" queryTableFieldId="8" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{18923D99-7B40-4DB3-A496-F76A3DD70196}" uniqueName="9" name="Total commission" queryTableFieldId="9" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{02516BDF-CDFA-4D06-A072-CBAABCE53FCD}" uniqueName="10" name="State" queryTableFieldId="10" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{2478EC7B-9201-464C-97D1-7832CCFDD2A3}" uniqueName="1" name="Order_Id" queryTableFieldId="1" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{02B1DDE7-04CB-444B-ABEF-B90EAE5BA784}" uniqueName="2" name="Date" queryTableFieldId="2" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{3C227B4A-8B12-4E4A-8F27-1A3C59A8F10F}" uniqueName="3" name="Item" queryTableFieldId="3" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{54E1CEE4-3B48-4D5A-8DA9-63C555A7FFFA}" uniqueName="4" name="Sales Rep" queryTableFieldId="4" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{9EC9992A-CB31-468E-9F69-4C965DD568D7}" uniqueName="5" name="Quantity" queryTableFieldId="5" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{6BB9D655-1011-4F3B-970D-80AB6F3EFBD8}" uniqueName="6" name="Price" queryTableFieldId="6" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{90CEDEA1-E2DB-4335-AD05-BC1C207AA4FB}" uniqueName="7" name="Total Sales" queryTableFieldId="7" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{BB982F64-1660-4B4F-B68D-2475B8D84B45}" uniqueName="8" name="Commission" queryTableFieldId="8" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{18923D99-7B40-4DB3-A496-F76A3DD70196}" uniqueName="9" name="Total commission" queryTableFieldId="9" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{02516BDF-CDFA-4D06-A072-CBAABCE53FCD}" uniqueName="10" name="State" queryTableFieldId="10" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -87713,7 +87566,7 @@
       <c r="A20" s="14">
         <v>43282</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="12">
         <v>50192</v>
       </c>
     </row>
@@ -87721,7 +87574,7 @@
       <c r="A21" s="14">
         <v>43283</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="12">
         <v>40738</v>
       </c>
     </row>
@@ -87729,7 +87582,7 @@
       <c r="A22" s="14">
         <v>43284</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="12">
         <v>34490</v>
       </c>
     </row>
@@ -87737,7 +87590,7 @@
       <c r="A23" s="14">
         <v>43285</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="12">
         <v>43812</v>
       </c>
     </row>
@@ -87745,7 +87598,7 @@
       <c r="A24" s="14">
         <v>43286</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="12">
         <v>63898</v>
       </c>
     </row>
@@ -87753,7 +87606,7 @@
       <c r="A25" s="14">
         <v>43287</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="12">
         <v>69418</v>
       </c>
     </row>
@@ -87761,7 +87614,7 @@
       <c r="A26" s="14">
         <v>43288</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="12">
         <v>76126</v>
       </c>
     </row>
@@ -87769,7 +87622,7 @@
       <c r="A27" s="14">
         <v>43289</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="12">
         <v>54420</v>
       </c>
     </row>
@@ -87777,7 +87630,7 @@
       <c r="A28" s="14">
         <v>43290</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="12">
         <v>38852</v>
       </c>
     </row>
@@ -87785,7 +87638,7 @@
       <c r="A29" s="14">
         <v>43291</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="12">
         <v>59360</v>
       </c>
     </row>
@@ -87793,7 +87646,7 @@
       <c r="A30" s="14">
         <v>43292</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="12">
         <v>45248</v>
       </c>
     </row>
@@ -87801,7 +87654,7 @@
       <c r="A31" s="14">
         <v>43293</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="12">
         <v>34652</v>
       </c>
     </row>
@@ -87809,7 +87662,7 @@
       <c r="A32" s="14">
         <v>43294</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="12">
         <v>44922</v>
       </c>
     </row>
@@ -87817,7 +87670,7 @@
       <c r="A33" s="14">
         <v>43295</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="12">
         <v>62620</v>
       </c>
     </row>
@@ -87825,7 +87678,7 @@
       <c r="A34" s="14">
         <v>43296</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="12">
         <v>40148</v>
       </c>
     </row>
@@ -87833,7 +87686,7 @@
       <c r="A35" s="14">
         <v>43297</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="12">
         <v>61950</v>
       </c>
     </row>
@@ -87841,7 +87694,7 @@
       <c r="A36" s="14">
         <v>43298</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="12">
         <v>37278</v>
       </c>
     </row>
@@ -87849,7 +87702,7 @@
       <c r="A37" s="14">
         <v>43299</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="12">
         <v>38752</v>
       </c>
     </row>
@@ -87857,7 +87710,7 @@
       <c r="A38" s="14">
         <v>43300</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="12">
         <v>64352</v>
       </c>
     </row>
@@ -87865,7 +87718,7 @@
       <c r="A39" s="14">
         <v>43301</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="12">
         <v>48100</v>
       </c>
     </row>
@@ -87873,7 +87726,7 @@
       <c r="A40" s="14">
         <v>43302</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="12">
         <v>53782</v>
       </c>
     </row>
@@ -87881,7 +87734,7 @@
       <c r="A41" s="14">
         <v>43303</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="12">
         <v>35948</v>
       </c>
     </row>
@@ -87889,7 +87742,7 @@
       <c r="A42" s="14">
         <v>43304</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="12">
         <v>50738</v>
       </c>
     </row>
@@ -87897,7 +87750,7 @@
       <c r="A43" s="14">
         <v>43305</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="12">
         <v>73018</v>
       </c>
     </row>
@@ -87905,7 +87758,7 @@
       <c r="A44" s="14">
         <v>43306</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="12">
         <v>66744</v>
       </c>
     </row>
@@ -87913,7 +87766,7 @@
       <c r="A45" s="14">
         <v>43307</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="12">
         <v>56284</v>
       </c>
     </row>
@@ -87921,7 +87774,7 @@
       <c r="A46" s="14">
         <v>43308</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="12">
         <v>74052</v>
       </c>
     </row>
@@ -87929,7 +87782,7 @@
       <c r="A47" s="14">
         <v>43309</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="12">
         <v>47276</v>
       </c>
     </row>
@@ -87937,7 +87790,7 @@
       <c r="A48" s="14">
         <v>43310</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="12">
         <v>52464</v>
       </c>
     </row>
@@ -87945,7 +87798,7 @@
       <c r="A49" s="14">
         <v>43311</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="12">
         <v>38450</v>
       </c>
     </row>
@@ -87953,7 +87806,7 @@
       <c r="A50" s="14">
         <v>43312</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="12">
         <v>27862</v>
       </c>
     </row>
@@ -87961,7 +87814,7 @@
       <c r="A51" s="14" t="s">
         <v>1342</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="12">
         <v>1585946</v>
       </c>
     </row>
@@ -87977,7 +87830,7 @@
       <c r="A55" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="12">
         <v>3071</v>
       </c>
     </row>
@@ -87985,7 +87838,7 @@
       <c r="A56" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="12">
         <v>2648</v>
       </c>
     </row>
@@ -87993,7 +87846,7 @@
       <c r="A57" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="12">
         <v>3833</v>
       </c>
     </row>
@@ -88001,7 +87854,7 @@
       <c r="A58" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="12">
         <v>3067</v>
       </c>
     </row>
@@ -88009,7 +87862,7 @@
       <c r="A59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="12">
         <v>4027</v>
       </c>
     </row>
@@ -88017,7 +87870,7 @@
       <c r="A60" s="12" t="s">
         <v>1342</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="12">
         <v>16646</v>
       </c>
     </row>
